--- a/windows_API.xlsx
+++ b/windows_API.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\박민준\컴퓨터 노하우\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AF26F3-0C47-4FF4-80E8-7E44D53CA39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6800EF-39F2-4492-BF52-B58D700A4556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">1. Windows SDK (Software Deveopment Kit) </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,6 +194,58 @@
   </si>
   <si>
     <t>프로젝트 생성(c++,Windows,Desktop 선택후 Windows Desktop Wizard 선택) &gt; Application type을 Desktop Application(exe) 선택, empty project 체크 후 &gt; 그후엔 여태까지 했던것과 동일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(10)공용화 코딩 : 한가지 코드로 여러가지 환경에 대응해서 자동빌드 되도록 짜는 코딩기법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(10-1) Windows API의 모든함수는 이 기법을 따른다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(11) 핸들(handle) : 객체(인스턴스)를 구별하는 식별자(주소값과는 다름) 만들때마다 O/S가 식별자 번호를 부여함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(11-1)핸들의 유형과 자료형 : HWND, HPEN, HBRUSH, HDC등이 있고 자료형은 대체로 구조체 포인터 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(12)옵션 매개변수 설정 방법 : Windows API에선 매개변수 하나당 두개이상의 값을 동시에 설정해야 하는 경우가 있음(중복선택) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이때 각 옵션을 하나의 매개변수의 인자로서 여러 개의 옵션값을 OR연산자로 묶어준다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(12-1)왜 옵션값을 OR연산자로 묶어야 하는가? : 옵션값이 이진값으로 볼떄 자릿수마다 하나의 옵션이 대응되게 설정 하기 때문이다(자릿값에 두개이상의 옵션값이 겹치면 원치않는 옵션도 중복적용 될 수 있기 때문에)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. Charcter set</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)역사적 흐름 : ASCII &gt; MBCS(Multi Byte Charcter Set) &gt; Unicode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)Windows API에선 MBCS 또는 Uincode중 한가지를 선택해서 사용해야함(default값은 unicode)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)MBCS와 Unicode의 리터럴 차이  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-1)mbcs 리터럴 : "~~~"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3-2)Unicode 리터럴 : L"~~~" //소문자 l적으면 에러남</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -475,6 +527,50 @@
         <a:xfrm>
           <a:off x="0" y="18783300"/>
           <a:ext cx="5496163" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>118325</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{962A9C37-FFE8-E6AE-4CA6-EC8E6029D0AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="23881080"/>
+          <a:ext cx="3848100" cy="1870925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -876,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE0ACE2-906B-4F5F-9E70-EA3E758911EF}">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -1065,6 +1161,41 @@
     <row r="101" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1207,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04728EDB-B3A1-4993-B993-BD89C0E92753}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -1087,6 +1218,36 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/windows_API.xlsx
+++ b/windows_API.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\박민준\컴퓨터 노하우\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6800EF-39F2-4492-BF52-B58D700A4556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628D71C9-05C2-4CE0-81CF-BE710F06188B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
   </bookViews>
   <sheets>
     <sheet name="기초개념" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="121">
   <si>
     <t xml:space="preserve">1. Windows SDK (Software Deveopment Kit) </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -197,56 +197,281 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(10)공용화 코딩 : 한가지 코드로 여러가지 환경에 대응해서 자동빌드 되도록 짜는 코딩기법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(10-1) Windows API의 모든함수는 이 기법을 따른다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(11) 핸들(handle) : 객체(인스턴스)를 구별하는 식별자(주소값과는 다름) 만들때마다 O/S가 식별자 번호를 부여함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(11-1)핸들의 유형과 자료형 : HWND, HPEN, HBRUSH, HDC등이 있고 자료형은 대체로 구조체 포인터 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(12)옵션 매개변수 설정 방법 : Windows API에선 매개변수 하나당 두개이상의 값을 동시에 설정해야 하는 경우가 있음(중복선택) </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이때 각 옵션을 하나의 매개변수의 인자로서 여러 개의 옵션값을 OR연산자로 묶어준다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(12-1)왜 옵션값을 OR연산자로 묶어야 하는가? : 옵션값이 이진값으로 볼떄 자릿수마다 하나의 옵션이 대응되게 설정 하기 때문이다(자릿값에 두개이상의 옵션값이 겹치면 원치않는 옵션도 중복적용 될 수 있기 때문에)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. Charcter set</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)역사적 흐름 : ASCII &gt; MBCS(Multi Byte Charcter Set) &gt; Unicode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(2)Windows API에선 MBCS 또는 Uincode중 한가지를 선택해서 사용해야함(default값은 unicode)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(3)MBCS와 Unicode의 리터럴 차이  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(3-1)mbcs 리터럴 : "~~~"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(3-2)Unicode 리터럴 : L"~~~" //소문자 l적으면 에러남</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>윈도우 O/S에서 비영어권 문자 표현을 위해 사용하는 방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cp949 같은것들 아스키형 char를 사용하는 C언어에서 문자열 리터럴("~")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저장시 사용하는 방식임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아스키 &gt; ansi &gt; MBCS &gt; 유니코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉, 아스키이후 유니코드가 제정되기전 사용되던 방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MBCS : "안녕"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNICODE : L"안녕"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MBCS : 2바이트 이상으로 문자를 표현하는 방식 그러나 유니코드가 아닌 ansi 방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. character set 설정하는법 : 프로젝트 우클릭 &gt; 프로퍼티 &gt; 어드밴시드 &gt; charcter set</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#define UNICODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#define _UNICODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 프로퍼티 창에서 문자열 설정을 유니코드로 설정하면 내부적으로 이와 같이 동작한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러면 window.h안에 정의되어 있는 각종 조건부 컴파일에 영향을 미치게 된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">예를 들어 MessageBox 함수의 경우 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[windows.h]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#ifdef UNICODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#define MessageBox MessageBoxW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#else</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#define MessageBox MessageBoxA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#endif</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>windows API는 기본적으로 함수명, 자료형 이름등에 대해 조건부 컴파일에 의한 공용화 방식으로 작성하고 있다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. procedure 함수 : 윈도우 메시지를 프로그램에서 받았을때 자동호출되는 함수(이 함수 안에서 그 이벤트에 대한 작업처리를 해준다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(5-1) 사용법 : 함수명은 중요하지않고, 리턴값의 자료형과 매개변수의 자료형과 개수만 일치하면 procedure 함수로 사용가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.Handle(식별자) 함수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의미 : 같은종류의 구조체 데이터를 구분하기 위해서 O/S가 부여한 고유의 정수값(구별을 위한 사용 주소와 같은 용도)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// P/G에서 사용하는 모든 데이터가 들어가 있는 구조체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>// HMODULE과 같은 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//커널용 구조체이기 떄문에 body는 비공개 형식적으로 볼 수 있는건 int unused 밖에 볼 수 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8. HWND = struct HWND__ *  구조체 포인터이며 같은 프로그램 내에서 여러 개의 창을 구분하기 위해 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.HINSTANCE = struct HINSTANCE __* //구조체 포인터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//창과 관련 모든 데이터를 가지고 있는 구조체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//커널용 구조체이므로  body는 비공개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9. 콘솔창 띄우기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AllocConsole(); </t>
+  </si>
+  <si>
+    <t>freopen("CONOUT$", "w", stdout);</t>
+  </si>
+  <si>
+    <t>2. 기본코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#include &lt;windows.h&gt;</t>
+  </si>
+  <si>
+    <t>#include &lt;stdio.h&gt;</t>
+  </si>
+  <si>
+    <t>LRESULT xx(HWND, WPARAM, LPARAM);</t>
+  </si>
+  <si>
+    <t>HINSTANCE g_hinst; //HINSTANCE를 wWinMain이 아닌곳에서도 쓰기 위해 전역변수로 정의</t>
+  </si>
+  <si>
+    <t>HWND hWndMain; //창에 대한 작업을 할 떄 가져다 쓰기 위해 전역변수로 정의</t>
+  </si>
+  <si>
+    <t>LPCTSTR lpszClass = L"하이"; //창의 캡션명, uni코드라서 L을 문자열 앞에 붙임</t>
+  </si>
+  <si>
+    <t>LPCTSTR lpszClass2 = L"윈도우클래스"; // 창의 식별자 이름 uni코드라서 L을 문자열 앞에 붙임</t>
+  </si>
+  <si>
+    <t>int APIENTRY wWinMain(HINSTANCE hinstance, HINSTANCE hPrevinstance, LPTSTR ipCmdLine, int nCmdShow) //2,3,4번쨰 매개변수는 형식적으로 넣고 1번째 매개변수인 인스턴스의 핸들값이 중요</t>
+  </si>
+  <si>
+    <t>{</t>
+  </si>
+  <si>
+    <t>freopen("CONOUT$", "w", stdout); // 13,14번째 줄은 그냥 콘솔창을 띄우기 위한 코드(printf등을 사용하기 위해서 써야함, 복붙으로 사용)</t>
+  </si>
+  <si>
+    <t>HWND hWnd;</t>
+  </si>
+  <si>
+    <t>MSG Message; //메시지 정보가 있는 구조체, getmessage 함수의 첫번째 "out"형(return과 유사) 매개변수에 사용해서 받아내기 위해 미리 선언</t>
+  </si>
+  <si>
+    <t>WNDCLASS WndClass;</t>
+  </si>
+  <si>
+    <t>g_hinst = hinstance;</t>
+  </si>
+  <si>
+    <t>WndClass.cbClsExtra = 0;</t>
+  </si>
+  <si>
+    <t>WndClass.cbWndExtra = 0;</t>
+  </si>
+  <si>
+    <t>WndClass.hbrBackground = (HBRUSH)GetStockObject(WHITE_BRUSH);</t>
+  </si>
+  <si>
+    <t>WndClass.hCursor = LoadCursorW(NULL, IDC_IBEAM);</t>
+  </si>
+  <si>
+    <t>WndClass.hIcon = LoadIconW(NULL, IDI_APPLICATION);</t>
+  </si>
+  <si>
+    <t>WndClass.hInstance = hinstance;</t>
+  </si>
+  <si>
+    <t>WndClass.lpfnWndProc = xx;</t>
+  </si>
+  <si>
+    <t>WndClass.lpszClassName = lpszClass2;</t>
+  </si>
+  <si>
+    <t>WndClass.lpszMenuName = NULL;</t>
+  </si>
+  <si>
+    <t>WndClass.style = CS_HREDRAW | CS_VREDRAW | CS_DBLCLKS;</t>
+  </si>
+  <si>
+    <t>RegisterClass(&amp;WndClass);</t>
+  </si>
+  <si>
+    <t>hWnd = CreateWindow(lpszClass2, lpszClass, WS_OVERLAPPEDWINDOW, CW_USEDEFAULT, CW_USEDEFAULT, CW_USEDEFAULT, CW_USEDEFAULT, NULL, NULL, g_hinst, NULL);</t>
+  </si>
+  <si>
+    <t>ShowWindow(hWnd, nCmdShow);</t>
+  </si>
+  <si>
+    <t>hWndMain = hWnd;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">while(GetMessage(&amp;Message, NULL, 0, 0)) </t>
+  </si>
+  <si>
+    <t>TranslateMessage(&amp;Message);</t>
+  </si>
+  <si>
+    <t>DispatchMessage(&amp;Message);</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>return (int)Message.wParam;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRESULT CALLBACK xx(HWND hWnd, UINT iMessage, WPARAM wParam, LPARAM lParam) </t>
+  </si>
+  <si>
+    <t>HDC hdc;</t>
+  </si>
+  <si>
+    <t>PAINTSTRUCT ps;</t>
+  </si>
+  <si>
+    <t>switch (iMessage) {</t>
+  </si>
+  <si>
+    <t>case WM_CREATE:</t>
+  </si>
+  <si>
+    <t>return 0;</t>
+  </si>
+  <si>
+    <t>case WM_PAINT:</t>
+  </si>
+  <si>
+    <t>hdc = BeginPaint(hWnd, &amp;ps);</t>
+  </si>
+  <si>
+    <t>EndPaint(hWnd, &amp;ps);</t>
+  </si>
+  <si>
+    <t>case WM_DESTROY:</t>
+  </si>
+  <si>
+    <t>PostQuitMessage(0);</t>
+  </si>
+  <si>
+    <t>return(DefWindowProc(hWnd, iMessage, wParam, lParam));</t>
   </si>
 </sst>
 </file>
@@ -527,50 +752,6 @@
         <a:xfrm>
           <a:off x="0" y="18783300"/>
           <a:ext cx="5496163" cy="800100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>118325</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{962A9C37-FFE8-E6AE-4CA6-EC8E6029D0AC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="23881080"/>
-          <a:ext cx="3848100" cy="1870925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -972,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE0ACE2-906B-4F5F-9E70-EA3E758911EF}">
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -1163,39 +1344,175 @@
         <v>37</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A102" t="s">
-        <v>40</v>
-      </c>
-    </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>51</v>
+      </c>
+      <c r="J113" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>52</v>
+      </c>
+      <c r="J114" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A131" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A132" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A135" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A136" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A137" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A139" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A140" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A141" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1207,7 +1524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04728EDB-B3A1-4993-B993-BD89C0E92753}">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -1220,34 +1537,274 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>47</v>
-      </c>
-    </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B45" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B46" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B50" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B55" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B57" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B59" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B61" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B62" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C63" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C64" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B65" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B67" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B72" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B73" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B75" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B76" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C77" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B78" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C79" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C80" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C81" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B82" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C83" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C84" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B85" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B86" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/windows_API.xlsx
+++ b/windows_API.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\박민준\컴퓨터 노하우\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628D71C9-05C2-4CE0-81CF-BE710F06188B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197223CF-8E22-4512-BEF6-D0F2506B7EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="136">
   <si>
     <t xml:space="preserve">1. Windows SDK (Software Deveopment Kit) </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -345,9 +345,6 @@
     <t>#include &lt;stdio.h&gt;</t>
   </si>
   <si>
-    <t>LRESULT xx(HWND, WPARAM, LPARAM);</t>
-  </si>
-  <si>
     <t>HINSTANCE g_hinst; //HINSTANCE를 wWinMain이 아닌곳에서도 쓰기 위해 전역변수로 정의</t>
   </si>
   <si>
@@ -375,9 +372,6 @@
     <t>MSG Message; //메시지 정보가 있는 구조체, getmessage 함수의 첫번째 "out"형(return과 유사) 매개변수에 사용해서 받아내기 위해 미리 선언</t>
   </si>
   <si>
-    <t>WNDCLASS WndClass;</t>
-  </si>
-  <si>
     <t>g_hinst = hinstance;</t>
   </si>
   <si>
@@ -387,66 +381,12 @@
     <t>WndClass.cbWndExtra = 0;</t>
   </si>
   <si>
-    <t>WndClass.hbrBackground = (HBRUSH)GetStockObject(WHITE_BRUSH);</t>
-  </si>
-  <si>
-    <t>WndClass.hCursor = LoadCursorW(NULL, IDC_IBEAM);</t>
-  </si>
-  <si>
-    <t>WndClass.hIcon = LoadIconW(NULL, IDI_APPLICATION);</t>
-  </si>
-  <si>
-    <t>WndClass.hInstance = hinstance;</t>
-  </si>
-  <si>
-    <t>WndClass.lpfnWndProc = xx;</t>
-  </si>
-  <si>
-    <t>WndClass.lpszClassName = lpszClass2;</t>
-  </si>
-  <si>
-    <t>WndClass.lpszMenuName = NULL;</t>
-  </si>
-  <si>
-    <t>WndClass.style = CS_HREDRAW | CS_VREDRAW | CS_DBLCLKS;</t>
-  </si>
-  <si>
-    <t>RegisterClass(&amp;WndClass);</t>
-  </si>
-  <si>
-    <t>hWnd = CreateWindow(lpszClass2, lpszClass, WS_OVERLAPPEDWINDOW, CW_USEDEFAULT, CW_USEDEFAULT, CW_USEDEFAULT, CW_USEDEFAULT, NULL, NULL, g_hinst, NULL);</t>
-  </si>
-  <si>
-    <t>ShowWindow(hWnd, nCmdShow);</t>
-  </si>
-  <si>
-    <t>hWndMain = hWnd;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">while(GetMessage(&amp;Message, NULL, 0, 0)) </t>
-  </si>
-  <si>
-    <t>TranslateMessage(&amp;Message);</t>
-  </si>
-  <si>
-    <t>DispatchMessage(&amp;Message);</t>
-  </si>
-  <si>
     <t>}</t>
   </si>
   <si>
-    <t>return (int)Message.wParam;</t>
-  </si>
-  <si>
     <t xml:space="preserve">LRESULT CALLBACK xx(HWND hWnd, UINT iMessage, WPARAM wParam, LPARAM lParam) </t>
   </si>
   <si>
-    <t>HDC hdc;</t>
-  </si>
-  <si>
-    <t>PAINTSTRUCT ps;</t>
-  </si>
-  <si>
     <t>switch (iMessage) {</t>
   </si>
   <si>
@@ -465,13 +405,122 @@
     <t>EndPaint(hWnd, &amp;ps);</t>
   </si>
   <si>
-    <t>case WM_DESTROY:</t>
-  </si>
-  <si>
-    <t>PostQuitMessage(0);</t>
-  </si>
-  <si>
-    <t>return(DefWindowProc(hWnd, iMessage, wParam, lParam));</t>
+    <t>10. 클라이언트  &amp; 윈도우 &amp; 스크린 좌표계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11. 비주얼 스튜디오에서 만든 실행파일 찾는법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exe를 찾아갈떈 Debug까지 경로를 복사한후 붙여넣는다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WNDCLASS WndClass; //윈도우 창 설정용 구조체</t>
+  </si>
+  <si>
+    <t>//창에 대한 설정 초기화 작업(윈도우 클래스 초기화)</t>
+  </si>
+  <si>
+    <t>WndClass.hbrBackground = (HBRUSH)GetStockObject(GRAY_BRUSH); //window 창 배경색(white,black,gray만 존재)</t>
+  </si>
+  <si>
+    <t>WndClass.hCursor = LoadCursorW(NULL, IDC_CROSS); //커서 모양 설정</t>
+  </si>
+  <si>
+    <t>WndClass.hIcon = LoadIconW(NULL, IDI_QUESTION); //캡션아이콘(창이름 옆에 있는) 설정</t>
+  </si>
+  <si>
+    <t>WndClass.hInstance = NULL; //창의 소속 설정 NULL은 값이 없다는게 아니라 기본값으로 설정</t>
+  </si>
+  <si>
+    <t>WndClass.lpfnWndProc = xx; //함수포인터, 프로시져 함수 설정용 멤버(아무 함수나 다 되는건 아니고 리턴값이 LRESULT이며 매개변수 4개짜리)</t>
+  </si>
+  <si>
+    <t>WndClass.lpszClassName = lpszClass2; //윈도우 창 클래스 이름 식별값이므로 중요</t>
+  </si>
+  <si>
+    <t>WndClass.lpszMenuName = NULL; //메뉴</t>
+  </si>
+  <si>
+    <t>WndClass.style = CS_HREDRAW | CS_VREDRAW | CS_DBLCLKS; // 옵션을 중복설정하고싶으면 |연산자로 묶어서 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RegisterClass(&amp;WndClass); //WndClass 등록 하는 법 : 레지스터클래스 함수에 WndClass 주소값 </t>
+  </si>
+  <si>
+    <t>hWnd = CreateWindow(lpszClass2, lpszClass, WS_OVERLAPPED | WS_CAPTION | WS_MAXIMIZEBOX | WS_SYSMENU | WS_MINIMIZEBOX, CW_USEDEFAULT,CW_USEDEFAULT,CW_USEDEFAULT,CW_USEDEFAULT, NULL, NULL, g_hinst, NULL);</t>
+  </si>
+  <si>
+    <t>//창을 여러개 만들수도 있으므로 창의 핸들값을 리턴 (첫번째 매개변수는 핸들명,두번째 매개변수가 캡션명(중요도X) 두개 순서 바뀌면 안됨)</t>
+  </si>
+  <si>
+    <t>//3번쨰 매개변수는 윈도우 창의 스타일을 설정 :  WS_OVERLAPPEDWINDOW는 6종을 모두 포함, 여러옵션을 사용할떈 |연산자 사용</t>
+  </si>
+  <si>
+    <t>//1,2번째 CW_USEDEFAULT 매개변수는 클라이언트 원점 좌표(각각 X,Y에 해당) 3,4번째는 창의 픽셀값(가로,세로 크기), CW는 CreateWindow약자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">//메모리에 창을 그리기떄문에 화면엔 아직 안보이는 상태 </t>
+  </si>
+  <si>
+    <t>ShowWindow(hWnd, nCmdShow); //만들어둔 창을 픽셀값으로 변환해서 모니터 화면에 출력하는 함수</t>
+  </si>
+  <si>
+    <t>hWndMain = hWnd; //핸들값 전달</t>
+  </si>
+  <si>
+    <t>while(GetMessage(&amp;Message, NULL, 0, 0)) //메시지 루프(WM_QUIT을 제외하곤 TRUE를 리턴함으로 메시지루프 바디실행)</t>
+  </si>
+  <si>
+    <t>TranslateMessage(&amp;Message); //현재 QUEUE에서 전달된 메시지 해석</t>
+  </si>
+  <si>
+    <t>DispatchMessage(&amp;Message); //프로시져 함수를 콜백시킴</t>
+  </si>
+  <si>
+    <t>//DispatchMessage에서 받은 메시지에 따라 switch - case문에 의해서 분기처리됨</t>
+  </si>
+  <si>
+    <t>HDC hdc; //그림그리기 위한 구조체(출력용)</t>
+  </si>
+  <si>
+    <t>PAINTSTRUCT ps; //팬이나 브러쉬같은 설정용 구조체</t>
+  </si>
+  <si>
+    <t>return 0; //break를 사용하면 switch case문을 빠져나가서 DefWindowProc()함수(모든 윈도우 메시지가 기본값으로 설정)가 호출됨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          //따라서 break가 아닌 return을 써서 프로시져 함수를 종료시켜서 DefWindowProc() 호출되지 않도록 처리해야함</t>
+  </si>
+  <si>
+    <t>case WM_DESTROY: //창의 X버튼을 누르면 WM_DESTORY를 발송됨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PostQuitMessage(0); // 얘를 호출하면 WM_QUIT이 발송됨. </t>
+  </si>
+  <si>
+    <t>//메시지루프의 GetMEssage()함수에서 WM_QUIT을 받으면 FALSE를 리턴하므로 메시지 루프 종료되면서 메인함수 종료 그래서 프로그램도 종료</t>
+  </si>
+  <si>
+    <t>return (DefWindowProc(hWnd, iMessage, wParam, lParam)); //switch - case에 해당하지 않으면 기본값으로 처리</t>
+  </si>
+  <si>
+    <t>실행파일은 debug와 release 두가지 종류가 있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LRESULT xx(HWND, WPARAM, LPARAM); //WPARAM,LPARAM에 부가정보가 저장되는데 메시지마다 부가정보의 내용이 다름</t>
+  </si>
+  <si>
+    <t>printf("%d", (int)Message.wParam);</t>
+  </si>
+  <si>
+    <t>//Sleep(10000); 메인스레드 홀드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">return (int)Message.wParam; //0이 찍히면(QUIT) 정상종료, 그외값은 비정상종료 </t>
   </si>
 </sst>
 </file>
@@ -517,9 +566,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,6 +592,66 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>640080</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="직사각형 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE6C58DE-793C-9670-DB55-32EBE6812B10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="640080" y="31481864"/>
+          <a:ext cx="8059972" cy="3709615"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -752,6 +864,1466 @@
         <a:xfrm>
           <a:off x="0" y="18783300"/>
           <a:ext cx="5496163" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>776</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>371460</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>168613</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09B36317-BF59-5693-B0BB-26F56BE12EAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1833770" y="31925263"/>
+          <a:ext cx="5899273" cy="3010428"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>518160</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="직선 화살표 연결선 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F88F7E6A-DA18-6012-136D-969FE0CFD795}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1188720" y="32430720"/>
+          <a:ext cx="624840" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="직선 화살표 연결선 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7441BA6-6A33-82BD-0F7A-AE15A82F0F41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1841390" y="32084507"/>
+          <a:ext cx="1391809" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>502228</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>502228</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="직선 화살표 연결선 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FC08ED4-AA0C-69BA-AEF3-4A2423DE7E57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1846119" y="32508998"/>
+          <a:ext cx="0" cy="1009304"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>658035</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>8586</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="TextBox 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A5C3A0D-BA30-D5AD-529D-AB6AEA04FA34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2936019" y="32038787"/>
+          <a:ext cx="398955" cy="331608"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>X</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>축</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>275294</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>77166</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="TextBox 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{302DE538-0AB9-9A81-9EBC-D94A87D7187D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1894730" y="32763350"/>
+          <a:ext cx="388268" cy="331607"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>y</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>축</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>434364</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>966</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="TextBox 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72A7590D-DDAB-ABDC-671C-51F0CE3B1F26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3917674" y="33561793"/>
+          <a:ext cx="1201333" cy="331608"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>클라이언트 영역</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>608412</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>203600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="TextBox 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EE86E9D-6E22-5F58-BAEA-DC1DF4EDE6E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="829255" y="32303168"/>
+          <a:ext cx="448392" cy="262241"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>(0,0)</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="직선 화살표 연결선 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1223139A-D915-59B6-32EC-9CD1D0796EF7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1841390" y="31911566"/>
+          <a:ext cx="1384189" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="854016" cy="336246"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="TextBox 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3FE21F4-062E-C1FF-EB60-1D7337C39DB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2464904" y="31593845"/>
+          <a:ext cx="854016" cy="336246"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>윈도우 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>X</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>축</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>316396</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>146107</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="844655" cy="336246"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="TextBox 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31842127-F578-09C9-4AF0-F3C1DE435D55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="985631" y="32945237"/>
+          <a:ext cx="844655" cy="336246"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>윈도우 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>y</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>축</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>480068</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>487688</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>194025</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="직선 화살표 연결선 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D28AE51-2235-E350-69D7-9CD443939551}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1823959" y="32348285"/>
+          <a:ext cx="7620" cy="1539995"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>583095</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>503582</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>165652</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="41" name="직선 화살표 연결선 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{343C257A-3A9A-6D0A-F770-64D03C751782}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1252330" y="32076887"/>
+          <a:ext cx="589722" cy="231913"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>629478</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>198783</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>510208</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>198783</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="43" name="직선 화살표 연결선 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F33F534F-DEE6-DD2B-8A34-C30631977003}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="629478" y="31467287"/>
+          <a:ext cx="1219200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>496956</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>205409</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>483704</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>125895</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="45" name="직선 화살표 연결선 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EADB0EB3-C06E-AFD3-53CC-F60F3C14AB0A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1166191" y="31911235"/>
+          <a:ext cx="655983" cy="357808"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>655983</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>132522</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1094787" cy="336246"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="TextBox 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04A738D3-8EB9-7D85-5483-4F13885736D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1325218" y="31619687"/>
+          <a:ext cx="1094787" cy="336246"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>윈도우 창 원점</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>629478</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>185531</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>629478</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>6626</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="48" name="직선 화살표 연결선 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A037338-5C15-1FAE-FE21-6A27013A7715}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="629478" y="31454035"/>
+          <a:ext cx="0" cy="1133061"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>106016</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>119270</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="854016" cy="336246"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="TextBox 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9858550-6B99-5D78-E8DE-B1926498CBB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1444486" y="31169113"/>
+          <a:ext cx="854016" cy="336246"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>스크린 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>X</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>축</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>26505</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="616226" cy="580159"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="TextBox 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19F17CF8-F8EE-9815-60A7-6934816E4E4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="31950992"/>
+          <a:ext cx="616226" cy="580159"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>스크린 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>y</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>축</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>13252</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>437322</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="직선 화살표 연결선 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7C85396-3F4D-7A4A-94E9-1E9A83542507}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="669235" y="31500417"/>
+          <a:ext cx="437322" cy="795131"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>172280</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>132522</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="616226" cy="580159"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="TextBox 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D417C8-A1A0-B8E8-E3DC-190AA3571488}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="172280" y="31182365"/>
+          <a:ext cx="616226" cy="580159"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>스크린 원점</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>666640</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>24390</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="그림 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA73F025-D737-7FA1-FDAE-EA6843944DC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="35641722"/>
+          <a:ext cx="14051336" cy="2648320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>536712</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>205409</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>371060</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>198782</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="직사각형 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{297D5669-8661-FB6C-8E58-B218AE5944A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1875182" y="37377757"/>
+          <a:ext cx="4518991" cy="212034"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>6626</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>192156</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>510208</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>13252</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="직선 화살표 연결선 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5038D6AC-7518-FB5B-03A0-BA090DA7417F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="675861" y="37583165"/>
+          <a:ext cx="1172817" cy="695739"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>649356</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>3799</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="그림 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B197D296-0EC2-085B-79AE-9E173F1900C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="38702974"/>
+          <a:ext cx="3995530" cy="1097103"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1153,7 +2725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE0ACE2-906B-4F5F-9E70-EA3E758911EF}">
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L177"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -1513,6 +3085,29 @@
     <row r="141" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A143" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B147" s="1"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A176" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A177" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1524,7 +3119,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04728EDB-B3A1-4993-B993-BD89C0E92753}">
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -1554,37 +3149,37 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
@@ -1594,217 +3189,267 @@
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B44" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B45" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B47" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B53" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B55" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B52" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B54" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B56" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B57" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.4">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B58" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B59" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B61" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B60" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B62" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C63" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C64" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B65" t="s">
-        <v>107</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B64" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B66" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B67" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A68" t="s">
-        <v>107</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C69" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A70" t="s">
-        <v>109</v>
+      <c r="C70" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A71" t="s">
-        <v>84</v>
+      <c r="B71" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B72" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B73" t="s">
-        <v>111</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B74" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B75" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B76" t="s">
-        <v>113</v>
+      <c r="A75" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C77" t="s">
-        <v>114</v>
+      <c r="A77" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B78" t="s">
-        <v>115</v>
+      <c r="A78" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C79" t="s">
-        <v>116</v>
+      <c r="A79" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C80" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C81" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B82" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C83" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C84" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B85" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B86" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A87" t="s">
-        <v>107</v>
+      <c r="B80" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B81" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B84" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C85" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C86" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B87" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C88" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C89" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C90" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B91" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C92" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C93" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B95" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B96" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/windows_API.xlsx
+++ b/windows_API.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\박민준\컴퓨터 노하우\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197223CF-8E22-4512-BEF6-D0F2506B7EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A28340-E0D3-490D-87AC-027989003CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
   </bookViews>
   <sheets>
     <sheet name="기초개념" sheetId="1" r:id="rId1"/>
-    <sheet name="기본 동작 방식" sheetId="2" r:id="rId2"/>
+    <sheet name="WM_MSG 정리" sheetId="3" r:id="rId2"/>
+    <sheet name="기본 동작 방식" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="170">
   <si>
     <t xml:space="preserve">1. Windows SDK (Software Deveopment Kit) </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -450,9 +451,6 @@
     <t xml:space="preserve">RegisterClass(&amp;WndClass); //WndClass 등록 하는 법 : 레지스터클래스 함수에 WndClass 주소값 </t>
   </si>
   <si>
-    <t>hWnd = CreateWindow(lpszClass2, lpszClass, WS_OVERLAPPED | WS_CAPTION | WS_MAXIMIZEBOX | WS_SYSMENU | WS_MINIMIZEBOX, CW_USEDEFAULT,CW_USEDEFAULT,CW_USEDEFAULT,CW_USEDEFAULT, NULL, NULL, g_hinst, NULL);</t>
-  </si>
-  <si>
     <t>//창을 여러개 만들수도 있으므로 창의 핸들값을 리턴 (첫번째 매개변수는 핸들명,두번째 매개변수가 캡션명(중요도X) 두개 순서 바뀌면 안됨)</t>
   </si>
   <si>
@@ -521,6 +519,146 @@
   </si>
   <si>
     <t xml:space="preserve">return (int)Message.wParam; //0이 찍히면(QUIT) 정상종료, 그외값은 비정상종료 </t>
+  </si>
+  <si>
+    <t>12. 윈도우창 용어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//update region : client 영역중에서 이동, 가려짐, 닫힘후 잠깐 화면에서 사라졌다가 다시 화면에 노출되었을때 다시 그리기작업(업데이트)이 필요한 영역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무효화 영역 (업데이트 영역)이 발생하면 윈도우는 프로그램에 WM_PAINT 메시지를 발송한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InvalidateRect() : WM_PAINT 발송 시키는 함수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//GDI(Graphic Device Interface) : 응용프로그램과 출력장치 사이의 인터페이스 담당. 현재는 GDI+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//gdi소속 함수들은 대부분 첫번째 매개변수로 HDC(Handle Device Context)를 요구함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Device Context : 출력에 필요한 모든 정보를 가지는 데이터 구조체. GDI 모듈에 의해 관리되는 데이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hWnd = CreateWindow(lpszClass2, lpszClass, WS_OVERLAPPEDWINDOW, CW_USEDEFAULT,CW_USEDEFAULT,CW_USEDEFAULT,CW_USEDEFAULT, NULL, NULL, g_hinst, NULL);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetDC(NULL) : 스크린 좌표계 기준의 DC를 반환함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetWindowDC(hWnd) : 윈도우 좌표계 기준의 DC를 반환함. 출력순서에 의해 글자가 안보일수도 있음 WM_NCPAINT 메시지에서 그려야함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wcslen(str) : 문자열의 길이를 반환(형변환은 직접 해줘야함)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TextOut(hdc,x값,y값,문자열(NULL문자 필요X),문자열의 길이) : 매개변수로 준 문자열의 길이만큼 문자열을 출력(문자열보다 문자열의 길이가 작으면 출력하다가 끊김, 크면 쓰레기값이 들어감)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReleaseDC(hWnd, hdc) : dc를 사용하고 난뒤 반환해주는 함수(반드시 사용후 반환 해야함)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. WM_LBUTTONDOWN : 마우스 왼쪽버튼이 눌렸을때 발송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만 window vista이후 DWM에서 자동복원 시킴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. WM_DESTORY : 창의 X버튼을 눌렀을때 발송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. WM_QUIT : PostQuitMessage(0)가 호출될때 발송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. WM_CREATE : 윈도우창이 처음 생겼을때 발송(Unity의 start이벤트 메서드랑 유사)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. WM_PAINT : 윈도우창이 처음 생길때 발송,무효화 영역이 생겼을때 자동발송, InvaildateRect()함수 호출시에는 강제 발송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetDC(hWnd) : 클라이언트 좌표계 기준의 DC를 반환함,메시지와 무관하게(PAINT에서도 사용가능) 아무데서나 사용가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EndPaint(hWnd, &amp;ps) : paint를 다 사용하고 작업종료시킬때 사용하는 함수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeginPaint(hWnd, &amp;ps) : paint 전용 DC얻어오는 함수(다른메시지에선 사용불가) 두번쨰 매개변수는 PAINTSTRUCT형 변수(그리기위한 정보가 있는 구조체)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetTextAlign(hdc,UNIT형 변수) : 정렬함수 hdc안에 정렬정보가 들어가고, 두번쨰 매개변수는 정렬옵션이다(비트연산으로 중복 적용가능), 기본값은 TA_TOP,TA_LEFT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정렬옵션은 교제 65P 참고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//TA_UPDATECP(current position) : 출력후 다음 출력위치는 마지막 출력 다음위치(시작위치도 0,0이기 때문에 좌표를 무시함)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">DrawText(HDC, LPCTSTR, int, LPRECT, UINT) : 텍스트 출력하는 함수  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetPixel(hdc,nXPos,nYPos,clrref) : 점 출력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LineTo(hdc,xEnd,yEnd) : 선출력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rectangle(hdc,left,top,right,bottom) : 사각형 출력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellipse(hdc,left,top,right,bottom) : 타원출력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CP(current position) : 출력 대기 위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveToEx(hdc, X값, Y값, NULL) : CP(current position)를 바꿔주는 함수, 선출력할떄도 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>함수에 붙은 EX의 의미 : 기존 함수를 확장한 새로운 함수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MessageBox(hWnd,str,str,UINT) : 메시지 박스 생성  마지막 매개변수는 버튼의 구성방식 설정 70P 참고( 아이콘과 버튼 구성방식은 OR연산자로 묶기 가능)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MessageBeep(UINT) : 소리 출력 함수 72P 참고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2332,6 +2470,344 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>184</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>185</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1" descr="생성된 이미지">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99DD2AE1-F5D5-0727-BD87-3C9D3CE314C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4023360" y="40660320"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>184</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>185</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="AutoShape 2" descr="생성된 이미지">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01FFD63A-3B62-8077-8FA2-A7FB05241FF2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4023360" y="40660320"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1027" name="AutoShape 3" descr="생성된 이미지">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{867F4BDD-917D-34EC-CC30-51EBD39544BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4693920" y="41323260"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>189</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>190</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1028" name="AutoShape 4" descr="생성된 이미지">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C476C64B-2F4D-CB6B-0D68-25D288A61004}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4693920" y="41765220"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>189</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>190</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1029" name="AutoShape 5" descr="생성된 이미지">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9D8AFE3-CD11-1C69-897A-B4D39124AD70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4693920" y="41765220"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>189</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>190</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1030" name="AutoShape 6" descr="생성된 이미지">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28D3D30F-8EA7-BC39-C6FD-0D968AE2276F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4693920" y="41765220"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>184</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>99393</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>99393</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE3CA29E-A1F7-FD26-E2A8-583AE2CF971D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="40233601"/>
+          <a:ext cx="2107096" cy="3160644"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2725,7 +3201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE0ACE2-906B-4F5F-9E70-EA3E758911EF}">
-  <dimension ref="A1:L177"/>
+  <dimension ref="A1:L242"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -3107,7 +3583,152 @@
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>131</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A184" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A200" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C201" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C202" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C203" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A204" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A205" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A206" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A208" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A209" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A210" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A212" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A214" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A216" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A218" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A220" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A222" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A223" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A224" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A225" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A227" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A228" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A230" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A232" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A234" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A236" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A238" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A240" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A242" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3118,6 +3739,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13244596-96F8-47E0-A9D7-E86B98AFFA18}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04728EDB-B3A1-4993-B993-BD89C0E92753}">
   <dimension ref="A1:C97"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
@@ -3149,7 +3806,7 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
@@ -3274,42 +3931,42 @@
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B56" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B57" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B58" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B59" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B60" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B64" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B66" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.4">
@@ -3319,12 +3976,12 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C69" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C70" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.4">
@@ -3334,17 +3991,17 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B72" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B73" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B74" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.4">
@@ -3359,7 +4016,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.4">
@@ -3369,12 +4026,12 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B80" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.4">
@@ -3389,12 +4046,12 @@
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C86" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.4">
@@ -3419,17 +4076,17 @@
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B91" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.4">
@@ -3444,7 +4101,7 @@
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B96" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">

--- a/windows_API.xlsx
+++ b/windows_API.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\박민준\컴퓨터 노하우\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A28340-E0D3-490D-87AC-027989003CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334742C9-D8F4-4D73-BF54-8FB2F6C9D420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="194">
   <si>
     <t xml:space="preserve">1. Windows SDK (Software Deveopment Kit) </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -533,10 +533,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>InvalidateRect() : WM_PAINT 발송 시키는 함수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>//GDI(Graphic Device Interface) : 응용프로그램과 출력장치 사이의 인터페이스 담당. 현재는 GDI+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -573,14 +569,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. WM_LBUTTONDOWN : 마우스 왼쪽버튼이 눌렸을때 발송</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>하지만 window vista이후 DWM에서 자동복원 시킴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3. WM_DESTORY : 창의 X버튼을 눌렀을때 발송</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -658,6 +646,114 @@
   </si>
   <si>
     <t>MessageBeep(UINT) : 소리 출력 함수 72P 참고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포커스(focus) : 활성상태에 있는 윈도우 창. 윈도우 O/S에선 동시에 여러 프로그램을 동작시킬수 있지만 오직 하나의 윈도우창만 포커스를 가질 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력과 출력 구분 : WM_PAINT에선 왠만하면 출력, WM_CHAR에선 입력을 하도록 권장된다(필수적으로 지키지 않아도됨)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8. WM_KEYUP : 키보드에서 눌린키가 때졌을때 발송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wParm에서 눌린키가 아스키코드값으로 저장 wParm을 통해 눌린키를 찾을 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문자열이 추가될때 수정하는 방법 : 76P 그림과 코드3줄 참고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">InvalidateRect(hWnd,NULL,TRUE) : WM_PAINT 발송 시키는 함수,2번째 매개변수가 NULL이라면 클라이언트 영역 전체를 무효화영역으로 다시그림, </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3번째 매개변수가 FALSE면 유지, TRUE는 삭제, 하지만 window vista이후 DWM에서 자동복원 시킴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rect 구조체를 사용해서 창의 일부만 다시 그리기 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. WM_CHAR : WM_KEYDOWN이 TranslateMessage(&amp;Message)가 처리한후 문자키면 호출(비문자키는 호출X)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.WM_KEYDOWN : 키보드에 있는 키를 누를때 발송(비문자키는 wParm에 가상 키값을 발송) 79~80P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TranslateMessage 함수 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키보드 키 'A'를 눌렀을때 메시지 발생 순서 : WM_KEYDOWN &gt; WM_CHAR &gt; WM_KEYUP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위의 3가지 메시지 중 사용자에 의해 직접 발생되는 메시지 : WM_KEYDOWN, WM_KEYUP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WM_CHAR 메시지 발생 원리 : WM_KEYDOWN 메시지 발생후 getMessage 함수에 의해 이 메시지가 TranslateMessage 함수로 전달된뒤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TranslateMessage 함수에서 문자가 발생한 경우로 식별된 경우에 하해 WM_CHAR 메시지를 발송하게 된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉 TranslateMessage함수가 호출되지 않으면 WM_CHAR는 발송되지 않는다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. WM_LBUTTONDOWN : 마우스 왼쪽버튼이 눌렸을때 발송, lParam에 마우스로 찍은 좌표값이 저장(HIWORD에 Y,LOWORD에 X), wParam에는 마우스 버튼이 눌릴때 같이 눌려진 키보드키를 저장(85P)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9. WM_MOUSEMOVE : 마우스가 (눌리든 안눌리든) 움직이면 발송(드래그와는 별개의 메시지)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더블클릭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS_DBLCLKS이 적용안되있을때 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS_DBLCLKS,이 적용되있을때:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WM_LBUTTONDOWN &gt; WM_LBUTTONUP &gt; WM_LBUTTONDOWN &gt; WM_LBUTTONUP </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WM_LBUTTONDOWN &gt; WM_LBUTTONUP &gt; WM_LBUTTONDBLCLK &gt; WM_BUTTONUP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마우스 입력 : 더블클릭을 인식 하려면 WndClass.style = CS_HREDRAW | CS_VREDRAW | CS_DBLCLKS; 이코드에서 CS_DBLCLKS이 포함되야 한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이머 : hTimer = (HANDLE)SetTimer(hWnd, 1, 1000, NULL); // SetTimer함수에서 타이머 생성(2번쨰 매개변수가 식별자,3번째 매개변수는 발생주기(단위는 밀리세컨드),)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wsprintf(sTime, L"지금 시간은 %d:%d:%d입니다", st.wHour, st.wMinute, st.wSecond); //첫번째 매개변수에 포멧대로 문자열을 만들어서 저장한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KillTimer(hWnd, 1); // 타이머를 다썻으면 KillTimer를 통해 없애야 한다(안없애면 자원낭비)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3201,7 +3297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE0ACE2-906B-4F5F-9E70-EA3E758911EF}">
-  <dimension ref="A1:L242"/>
+  <dimension ref="A1:L271"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -3603,132 +3699,227 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C202" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C203" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A204" t="s">
-        <v>139</v>
+      <c r="C204" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A208" t="s">
-        <v>154</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A207" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A211" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A213" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A215" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A212" t="s">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A217" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A214" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A216" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A218" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A220" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A222" t="s">
-        <v>157</v>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A219" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A221" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A227" t="s">
-        <v>166</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A226" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A230" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A229" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A231" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A233" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A235" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A232" t="s">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A237" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A234" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A236" t="s">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A239" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A238" t="s">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A241" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A243" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A245" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A240" t="s">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A247" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A242" t="s">
-        <v>169</v>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A249" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A251" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A252" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A253" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A254" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A255" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A256" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A258" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A260" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A261" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A262" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A264" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A265" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A267" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A269" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A271" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3740,32 +3931,77 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13244596-96F8-47E0-A9D7-E86B98AFFA18}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A271"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A258" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A267" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A269" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A271" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3931,7 +4167,7 @@
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B56" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.4">

--- a/windows_API.xlsx
+++ b/windows_API.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\박민준\컴퓨터 노하우\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334742C9-D8F4-4D73-BF54-8FB2F6C9D420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC6B6C1-BD49-4199-9CEE-23BF4FEBB5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
   </bookViews>
   <sheets>
     <sheet name="기초개념" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="197">
   <si>
     <t xml:space="preserve">1. Windows SDK (Software Deveopment Kit) </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -754,6 +754,18 @@
   </si>
   <si>
     <t>KillTimer(hWnd, 1); // 타이머를 다썻으면 KillTimer를 통해 없애야 한다(안없애면 자원낭비)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LRESULT의 자료형은 long long과 같음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//w를 앞에 붙이는 이유는 유니코드를 사용하기 위해서(즉, 안붙여도 동작은 됨) 매크로(조건부 컴파일이 안되있기 때문에)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로그램의 인스턴스 그자체.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4012,7 +4024,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04728EDB-B3A1-4993-B993-BD89C0E92753}">
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -4025,54 +4037,63 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="M25" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="J26" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>83</v>
+      </c>
+      <c r="B32" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">

--- a/windows_API.xlsx
+++ b/windows_API.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC6B6C1-BD49-4199-9CEE-23BF4FEBB5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C322BC5-99B5-4F69-A457-426250D3331C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="247">
   <si>
     <t xml:space="preserve">1. Windows SDK (Software Deveopment Kit) </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -581,10 +581,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2. WM_PAINT : 윈도우창이 처음 생길때 발송,무효화 영역이 생겼을때 자동발송, InvaildateRect()함수 호출시에는 강제 발송</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GetDC(hWnd) : 클라이언트 좌표계 기준의 DC를 반환함,메시지와 무관하게(PAINT에서도 사용가능) 아무데서나 사용가능</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -609,10 +605,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">DrawText(HDC, LPCTSTR, int, LPRECT, UINT) : 텍스트 출력하는 함수  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SetPixel(hdc,nXPos,nYPos,clrref) : 점 출력</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -669,10 +661,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">InvalidateRect(hWnd,NULL,TRUE) : WM_PAINT 발송 시키는 함수,2번째 매개변수가 NULL이라면 클라이언트 영역 전체를 무효화영역으로 다시그림, </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3번째 매개변수가 FALSE면 유지, TRUE는 삭제, 하지만 window vista이후 DWM에서 자동복원 시킴</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -766,6 +754,176 @@
   </si>
   <si>
     <t>프로그램의 인스턴스 그자체.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클라이언트 영역이 아닌 부분은 NC영역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. textout 예제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hdc = GetDC(hWnd);</t>
+  </si>
+  <si>
+    <t>TextOut(hdc, 100, 100, L"Ko", (int)wcslen(L"Ko"));</t>
+  </si>
+  <si>
+    <t>ReleaseDC(hWnd, hdc);</t>
+  </si>
+  <si>
+    <t>2. WM_PAINT : 윈도우창이 처음 생길때 발송(WM_CREATE 이후에 발송),무효화 영역이 생겼을때 자동발송, InvaildateRect()함수 호출시에는 강제 발송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DrawText(HDC, LPCTSTR, int, LPRECT, UINT) : 텍스트 출력하는 함수(TextOut보다 기능이 많음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)옵션 : DT_WORKBREAK 문자열의 마지막에 띄어쓰기가 되있으면 줄바꿈이 된다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WCHAR str[] = L"abcsdsdsdsddssdsddsdsdsddssdd "</t>
+  </si>
+  <si>
+    <t xml:space="preserve">efsdsdsddssddssdsdsdsdsddssddssddsdssddssdsdgh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">hidsdssdsdsddsdsdssdsddssdsddssdsdjk </t>
+  </si>
+  <si>
+    <t>lmsddfsidhlhsdfhdshfksdjfhsjfhlsdhfkshdksdhfskno ;</t>
+  </si>
+  <si>
+    <t>LRESULT CALLBACK xx(HWND hWnd, UINT iMessage, WPARAM wParam, LPARAM lParam)</t>
+  </si>
+  <si>
+    <t>RECT rt = { 100,100,400,300 };</t>
+  </si>
+  <si>
+    <t>//따라서 break가 아닌 return을 써서 프로시져 함수를 종료시켜서 DefWindowProc() 호출되지 않도록 처리해야함</t>
+  </si>
+  <si>
+    <t>//hdc = GetDC(hWnd);</t>
+  </si>
+  <si>
+    <t>DrawText(hdc, str, -1, &amp;rt, DT_CENTER | DT_WORDBREAK);</t>
+  </si>
+  <si>
+    <t>//ReleaseDC(hWnd, hdc);</t>
+  </si>
+  <si>
+    <t>EndPaint(hWnd, hdc);</t>
+  </si>
+  <si>
+    <t>// -1을 넣은 이유는 널문자로 끝나는 문자열이란걸 표시(길이지정을 따로 안해도 됨 널문자로 끝나는 문자열이 아니면 wcslen()을 통해 처리)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)주의사항 : 메시지박스가 죽기전까진 다른 메시지 처리가 불가능하다(우회방법있음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>case WM_LBUTTONDOWN:</t>
+  </si>
+  <si>
+    <t>MessageBox(hWnd, L"클릭", L"메시지박스", MB_OK);</t>
+  </si>
+  <si>
+    <t>4.WM_CHAR 예제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>static WCHAR str[256]; //static선언이 되어서 초기값을 지정안하면 0으로 초기화</t>
+  </si>
+  <si>
+    <t>int len;</t>
+  </si>
+  <si>
+    <t>case WM_CHAR:</t>
+  </si>
+  <si>
+    <t>if ((WCHAR)wParam == 32) //아스키코드값 32번은 스페이스바</t>
+  </si>
+  <si>
+    <t>str[0] = 0;</t>
+  </si>
+  <si>
+    <t>else {</t>
+  </si>
+  <si>
+    <t>len = wcslen(str); //str이 static선언되있기 떄문에 쓰레기값이 아닌 0이 들어감</t>
+  </si>
+  <si>
+    <t>printf("%d", len);</t>
+  </si>
+  <si>
+    <t>str[len] = (WCHAR)wParam;</t>
+  </si>
+  <si>
+    <t>str[len + 1] = 0;</t>
+  </si>
+  <si>
+    <t>InvalidateRect(hWnd, NULL, TRUE);</t>
+  </si>
+  <si>
+    <t>TextOut(hdc, 100, 100, str, wcslen(str));</t>
+  </si>
+  <si>
+    <t>InvalidateRect(hWnd,NULL,TRUE) : WM_PAINT 발송 시키는 함수,2번째 매개변수가 NULL이라면 클라이언트 영역 전체를 무효화영역으로 다시그림, 3번째매개변수는 bErase 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bErase : 무효화되기 전 배경을 모두 지우고 다시 그릴지 아니면 지우지 않고 덮어쓰기 할지 지정(TRUE면 배경을 지운후 다시 그림,FALSE면 배경을 덮어쓰기)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>static int x, y;</t>
+  </si>
+  <si>
+    <t>static BOOL bnowDraw = FALSE;</t>
+  </si>
+  <si>
+    <t>x = LOWORD(lParam); // 현재위치값을 lParam이 가지고 있기 때문에 LOWORD,HIWORD로 추출</t>
+  </si>
+  <si>
+    <t>y = HIWORD(lParam);</t>
+  </si>
+  <si>
+    <t>bnowDraw = TRUE;</t>
+  </si>
+  <si>
+    <t>case WM_MOUSEMOVE:</t>
+  </si>
+  <si>
+    <t>if (bnowDraw == TRUE) {</t>
+  </si>
+  <si>
+    <t>MoveToEx(hdc, x, y, NULL);</t>
+  </si>
+  <si>
+    <t>x = LOWORD(lParam);</t>
+  </si>
+  <si>
+    <t>LineTo(hdc, x, y);</t>
+  </si>
+  <si>
+    <t>case WM_LBUTTONUP:</t>
+  </si>
+  <si>
+    <t>bnowDraw = FALSE;</t>
+  </si>
+  <si>
+    <t>TextOut(hdc,x,y,"A",1);</t>
+  </si>
+  <si>
+    <t>case WM_LBUTTONDBLCLK:</t>
+  </si>
+  <si>
+    <t>5.WM_MOUSEMOVE ,WM_LBUTTONDBLCLK예제 (더블클릭 판별하려면 wndClass style에서 CS_DBLCLKS를 추가해야한다)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2916,6 +3074,62 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>19878</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>99392</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>563217</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>92765</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="직선 화살표 연결선 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{309E83C0-3FE7-FEA1-1D45-893AEDD4CD0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6042991" y="31149235"/>
+          <a:ext cx="543339" cy="868017"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx2"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3309,7 +3523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE0ACE2-906B-4F5F-9E70-EA3E758911EF}">
-  <dimension ref="A1:L271"/>
+  <dimension ref="A1:L316"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -3621,59 +3835,62 @@
         <v>64</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
         <v>98</v>
+      </c>
+      <c r="K143" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.4">
@@ -3711,227 +3928,400 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C202" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C203" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C204" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A205" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C208" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C209" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A210" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A206" t="s">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A211" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A207" t="s">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A212" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A209" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A210" t="s">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A214" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A215" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A211" t="s">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A216" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A213" t="s">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A218" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A215" t="s">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A220" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A217" t="s">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A222" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A219" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A221" t="s">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A224" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A223" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A224" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A225" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>159</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A230" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A235" t="s">
-        <v>160</v>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A234" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A236" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>161</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A238" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A240" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="241" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B241" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="242" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B242" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="243" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B243" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="244" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B244" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="245" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="C245" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="246" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="C246" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="247" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="C247" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="249" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B249" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="250" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B250" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="251" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="C251" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="252" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="C252" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="253" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B253" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="254" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="C254" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="255" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="C255" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="256" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="C256" t="s">
+        <v>210</v>
+      </c>
+      <c r="I256" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C257" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C258" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C259" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B261" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C262" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C263" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C264" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B266" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B268" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A269" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A275" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A277" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A279" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A281" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A283" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A284" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A285" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B286" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B287" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A288" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A241" t="s">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A290" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A243" t="s">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A292" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A245" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A247" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A249" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A251" t="s">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A294" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A296" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A297" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A298" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A299" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A252" t="s">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A300" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A253" t="s">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A301" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A254" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A255" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A256" t="s">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A303" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A305" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A258" t="s">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A306" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A307" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A309" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A310" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A312" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A314" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A316" t="s">
         <v>190</v>
-      </c>
-    </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A260" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A261" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A262" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A264" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A265" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A267" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A269" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A271" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3943,17 +4333,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13244596-96F8-47E0-A9D7-E86B98AFFA18}">
-  <dimension ref="A1:A271"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
@@ -3973,47 +4363,27 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A258" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A267" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A269" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A271" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -4024,7 +4394,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04728EDB-B3A1-4993-B993-BD89C0E92753}">
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M193"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -4057,7 +4427,7 @@
         <v>131</v>
       </c>
       <c r="M25" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -4065,7 +4435,7 @@
         <v>78</v>
       </c>
       <c r="J26" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -4093,7 +4463,7 @@
         <v>83</v>
       </c>
       <c r="B32" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
@@ -4361,8 +4731,438 @@
         <v>129</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B108" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B109" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B110" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B111" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B112" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B113" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C114" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C115" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B116" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C117" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C118" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D119" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C120" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C121" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D122" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D123" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D124" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D125" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C126" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C127" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C128" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B129" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C130" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C131" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C132" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C133" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B135" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C136" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C137" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C138" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B140" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B142" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A143" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A145" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A146" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A147" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A148" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B149" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B150" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B151" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B152" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B153" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B154" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C155" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C156" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B157" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C158" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C159" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C160" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C161" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B162" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C163" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D164" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D165" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D166" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D167" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D168" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D169" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B170" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C171" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B172" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C173" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C174" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B175" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C176" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C177" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B178" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C179" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C180" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="181" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C181" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C182" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B184" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C185" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C186" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C187" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B189" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B192" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A193" t="s">
         <v>90</v>
       </c>
     </row>

--- a/windows_API.xlsx
+++ b/windows_API.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C322BC5-99B5-4F69-A457-426250D3331C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920226A5-E6F0-48C6-8DAE-36FFD30797EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
   </bookViews>
   <sheets>
     <sheet name="기초개념" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="291">
   <si>
     <t xml:space="preserve">1. Windows SDK (Software Deveopment Kit) </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -733,10 +733,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>타이머 : hTimer = (HANDLE)SetTimer(hWnd, 1, 1000, NULL); // SetTimer함수에서 타이머 생성(2번쨰 매개변수가 식별자,3번째 매개변수는 발생주기(단위는 밀리세컨드),)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>wsprintf(sTime, L"지금 시간은 %d:%d:%d입니다", st.wHour, st.wMinute, st.wSecond); //첫번째 매개변수에 포멧대로 문자열을 만들어서 저장한다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -873,10 +869,6 @@
     <t>TextOut(hdc, 100, 100, str, wcslen(str));</t>
   </si>
   <si>
-    <t>InvalidateRect(hWnd,NULL,TRUE) : WM_PAINT 발송 시키는 함수,2번째 매개변수가 NULL이라면 클라이언트 영역 전체를 무효화영역으로 다시그림, 3번째매개변수는 bErase 설정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bErase : 무효화되기 전 배경을 모두 지우고 다시 그릴지 아니면 지우지 않고 덮어쓰기 할지 지정(TRUE면 배경을 지운후 다시 그림,FALSE면 배경을 덮어쓰기)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -924,6 +916,154 @@
   </si>
   <si>
     <t>5.WM_MOUSEMOVE ,WM_LBUTTONDBLCLK예제 (더블클릭 판별하려면 wndClass style에서 CS_DBLCLKS를 추가해야한다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InvalidateRect(hWnd,NULL,TRUE) : WM_PAINT 발송 시키는 함수,2번째 매개변수가 NULL이라면(NULL이 아니면 RECT 구조체 영역만 무효화 영역) 클라이언트 영역 전체를 무효화영역으로 다시그림, 3번째매개변수는 bErase 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.WM_TIMER : setTimer()함수의 3번째 매개변수 시간마다 발송되고 killTimer 전까지 계속 발송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. 타이머 예제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>static HANDLE hTimer; //포인터</t>
+  </si>
+  <si>
+    <t>SYSTEMTIME st; //시간정보를 담고 있는 구조체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">static WCHAR sTime[128]; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">hTimer = (HANDLE)SetTimer(hWnd, 1, 1000, NULL); //2번째가 타이머 식별값 3번째는 타이머 발생주기 </t>
+  </si>
+  <si>
+    <t>case WM_TIMER:</t>
+  </si>
+  <si>
+    <t>GetLocalTime(&amp;st); // 현재 pc의 시간정보를 받아서 st에 저장</t>
+  </si>
+  <si>
+    <t>wsprintf(sTime, L"지금 시간은 %d%d%d",  st.wHour, st.wMinute,st.wSecond); //저포멧대로 sTime에 저장</t>
+  </si>
+  <si>
+    <t>InvalidateRect(hWnd, NULL, TRUE); // WM_PAINT를 발송하기 위해서 InvalidateRect를 호출</t>
+  </si>
+  <si>
+    <t>TextOut(hdc, 100, 100, sTime, wcslen(sTime));</t>
+  </si>
+  <si>
+    <t>KillTimer(hWnd, 1); //사용을 다했으면 killTimer를 통해 제거(2번째 매개변수에 setTimer때 썻던 식별자값을 입력)</t>
+  </si>
+  <si>
+    <t>//static RECT rt = {100,100,400,120};</t>
+  </si>
+  <si>
+    <t>//SendMessage(hWnd, WM_TIMER, 1, 0); // 강제발송(setTimer가 호출될땐 발송이 안되기때문에 호출될때 발송을 하기위해)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">//InvalidateRect(hWnd, &amp;rt, TRUE); //클라이언트 영역 전체가 아니라 rt의 범위만큼 무효화 영역 </t>
+  </si>
+  <si>
+    <t>6-1 다중 타이머 예시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>static HANDLE hTimer,hTimer2; //포인터</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hTimer2 = (HANDLE)SetTimer(hWnd, 10, 5000, NULL); </t>
+  </si>
+  <si>
+    <t>switch (wParam) { //wParam이 타이머의 식별자값을 저장</t>
+  </si>
+  <si>
+    <t>case 1:</t>
+  </si>
+  <si>
+    <t>wsprintf(sTime, L"지금 시간은 %d%d%d", st.wHour, st.wMinute, st.wSecond); //저포멧대로 sTime에 저장</t>
+  </si>
+  <si>
+    <t>break;</t>
+  </si>
+  <si>
+    <t>case 10:</t>
+  </si>
+  <si>
+    <t>MessageBeep(0);</t>
+  </si>
+  <si>
+    <t>KillTimer(hWnd, 10);</t>
+  </si>
+  <si>
+    <t>SendMessage(hWnd,메시지 종류,wParam,lParam) : 해당하는 메시지를 강제 발송(3,4번째엔 wParam,lParam값을 매개변수로 넘김) 또한 리턴값이 프로시져 함수와 같다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이머 : hTimer = (HANDLE)SetTimer(hWnd, 1, 1000, NULL); // SetTimer함수에서 타이머 생성(2번쨰 매개변수가 식별자,3번째 매개변수는 발생주기(단위는 밀리세컨드),4번째 매개변수는 딜레이 간격으로 호출될 함수의 이름(함수포인터))</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. 콜백 함수 예제(메시지 내부에서 무한루프 처리 X)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>void CALLBACK TimerProc(HWND hWnd, UINT idEvent, DWORD dwTime) //setTimer의 4번째 매개변수로 설정하는 함수는 이 원형으로 만들어야한다</t>
+  </si>
+  <si>
+    <t>{//TimeProc로 반복작업을 처리한 이유는 메시지 내부에서 무한루프를 하게되면 그 메시지가 안끝나므로 다른 메시지를 처리할 수 없다</t>
+  </si>
+  <si>
+    <t>HDC hdc;</t>
+  </si>
+  <si>
+    <t>int i;</t>
+  </si>
+  <si>
+    <t>for (i = 0;i &lt; 100;i++) {</t>
+  </si>
+  <si>
+    <t>SetPixel(hdc, rand() % 500, rand() % 400, RGB(rand() % 256, rand() % 256, rand() % 256));</t>
+  </si>
+  <si>
+    <t>SetTimer(hWnd, 1, 100, (TIMERPROC)TimerProc); //4번째 매개변수로 함수를 호출할 수 있다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">return 0; </t>
+  </si>
+  <si>
+    <t>InvalidateRect(hWnd, NULL,FALSE);</t>
+  </si>
+  <si>
+    <t>/*int i;</t>
+  </si>
+  <si>
+    <t>for (;;) { 반복작업을 해야할땐 메시지 내부에서 하면 안된다(메시지가 안끝나므로 다른메시지를 수용할 수 없다)</t>
+  </si>
+  <si>
+    <t>//sleep을 넣어준다 해도 WM_PAINT가 안끝나므로 해결X</t>
+  </si>
+  <si>
+    <t>}*/</t>
+  </si>
+  <si>
+    <t>KillTimer(hWnd, 1);</t>
+  </si>
+  <si>
+    <t>메시지 내부에서 무한반복을 돌리면 안되는 이유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메시지 내부에서 무한루프를 돌리면 그 메시지가 안끝나므로 다른 메시지를 받을수 없다 그러므로 적어도 메인쓰레드(사용자와 상호작용 쓰레드)에선 메시지 내부에 무한 루프를 돌리면 안된다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정 돌려야한다면 별도의 쓰레드를 만들어서 다른 쓰레드에서 돌려야 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3523,7 +3663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE0ACE2-906B-4F5F-9E70-EA3E758911EF}">
-  <dimension ref="A1:L316"/>
+  <dimension ref="A1:L322"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -3890,7 +4030,7 @@
         <v>98</v>
       </c>
       <c r="K143" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.4">
@@ -3928,12 +4068,12 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C202" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C203" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.4">
@@ -4033,17 +4173,17 @@
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.4">
@@ -4068,27 +4208,27 @@
     </row>
     <row r="243" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B243" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="244" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B244" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="245" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C245" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="246" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C246" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="247" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C247" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="249" spans="2:9" x14ac:dyDescent="0.4">
@@ -4108,7 +4248,7 @@
     </row>
     <row r="252" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C252" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="253" spans="2:9" x14ac:dyDescent="0.4">
@@ -4118,7 +4258,7 @@
     </row>
     <row r="254" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C254" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="255" spans="2:9" x14ac:dyDescent="0.4">
@@ -4128,20 +4268,20 @@
     </row>
     <row r="256" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C256" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I256" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C257" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C258" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.4">
@@ -4211,17 +4351,17 @@
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B286" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.4">
@@ -4311,17 +4451,37 @@
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
-        <v>188</v>
+        <v>272</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A316" t="s">
-        <v>190</v>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A318" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A320" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A321" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A322" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -4333,7 +4493,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13244596-96F8-47E0-A9D7-E86B98AFFA18}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -4343,7 +4503,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
@@ -4384,6 +4544,11 @@
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -4394,7 +4559,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04728EDB-B3A1-4993-B993-BD89C0E92753}">
-  <dimension ref="A1:M193"/>
+  <dimension ref="A1:M321"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -4427,7 +4592,7 @@
         <v>131</v>
       </c>
       <c r="M25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -4435,7 +4600,7 @@
         <v>78</v>
       </c>
       <c r="J26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -4463,7 +4628,7 @@
         <v>83</v>
       </c>
       <c r="B32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
@@ -4738,32 +4903,32 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.4">
@@ -4788,12 +4953,12 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B110" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B111" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.4">
@@ -4813,17 +4978,17 @@
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C115" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B116" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C117" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.4">
@@ -4833,7 +4998,7 @@
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D119" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.4">
@@ -4843,27 +5008,27 @@
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C121" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D122" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D123" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D124" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D125" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.4">
@@ -4873,7 +5038,7 @@
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C127" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="128" spans="2:4" x14ac:dyDescent="0.4">
@@ -4893,7 +5058,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C131" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.4">
@@ -4943,12 +5108,12 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.4">
@@ -4973,12 +5138,12 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B151" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B152" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.4">
@@ -4998,27 +5163,27 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C156" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B157" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C158" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C159" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C160" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.4">
@@ -5028,42 +5193,42 @@
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B162" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C163" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D164" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D165" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D166" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D167" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D168" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D169" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.4">
@@ -5078,12 +5243,12 @@
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B172" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C173" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.4">
@@ -5093,12 +5258,12 @@
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B175" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C176" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.4">
@@ -5118,7 +5283,7 @@
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C180" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.4">
@@ -5161,8 +5326,598 @@
         <v>129</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A195" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A196" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A197" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A198" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B199" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B200" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B201" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B202" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B203" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B204" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B206" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B207" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C208" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C209" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C210" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C211" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B212" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="213" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C213" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="214" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C214" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="215" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C215" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="216" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C216" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="217" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C217" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="218" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B218" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="219" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C219" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="220" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C220" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C221" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="222" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C222" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B223" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="224" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C224" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C225" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C226" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C227" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B228" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B229" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A230" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A232" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A233" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A234" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A235" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B236" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B237" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B238" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B239" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B240" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="241" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B241" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="243" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B243" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="244" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B244" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="245" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C245" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="246" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C246" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="247" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C247" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="248" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C248" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="249" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C249" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="250" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C251" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="252" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C252" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="253" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D253" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="254" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D254" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="255" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D255" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="256" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D256" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="257" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C257" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="258" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D258" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="259" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D259" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="260" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C260" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="262" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C262" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="263" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C263" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="264" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B264" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="265" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C265" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="266" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C266" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="267" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C267" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="268" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C268" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="269" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B269" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="270" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C270" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="271" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C271" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C272" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C273" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C274" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B275" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B276" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A277" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A279" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A280" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A281" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B282" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B283" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B284" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B285" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C286" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B287" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B288" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A289" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A292" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A293" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A294" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B295" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B296" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B299" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B300" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C301" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C302" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B303" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C304" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="305" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B305" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="306" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C306" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="307" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C307" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="308" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C308" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="309" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D309" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="310" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D310" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="311" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C311" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="312" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C312" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="313" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C313" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="314" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B314" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="315" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C315" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="316" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C316" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="317" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C317" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="318" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C318" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="319" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B319" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="320" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B320" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A321" t="s">
         <v>90</v>
       </c>
     </row>

--- a/windows_API.xlsx
+++ b/windows_API.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920226A5-E6F0-48C6-8DAE-36FFD30797EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2FF26F-92C4-4DE5-B25B-273E64E1ABD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
   </bookViews>
   <sheets>
     <sheet name="기초개념" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="323">
   <si>
     <t xml:space="preserve">1. Windows SDK (Software Deveopment Kit) </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -923,10 +923,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.WM_TIMER : setTimer()함수의 3번째 매개변수 시간마다 발송되고 killTimer 전까지 계속 발송</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>6. 타이머 예제</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1065,6 +1061,108 @@
   <si>
     <t>정 돌려야한다면 별도의 쓰레드를 만들어서 다른 쓰레드에서 돌려야 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//wParam :  타이머 식별자값(setTimer()함수 호출시 2번째 매개변수)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.WM_TIMER : setTimer()함수의 3번째 매개변수 시간마다 발송되고 killTimer 전까지 계속 발송(wParam :  타이머 식별자값(setTimer()함수 호출시 2번째 매개변수))</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8. 프로시저 작업을 메인에서 처리하는 타이머 예제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LRESULT의 자료형은 long long과 같음</t>
+  </si>
+  <si>
+    <t>프로그램의 인스턴스 그자체.</t>
+  </si>
+  <si>
+    <t>HANDLE hTimer, hTimer2;</t>
+  </si>
+  <si>
+    <t>int CALLBACK wWinMain(HINSTANCE hinstance, HINSTANCE hPrevinstance, LPTSTR ipCmdLine, int nCmdShow) //2,3,4번쨰 매개변수는 형식적으로 넣고 1번째 매개변수인 인스턴스의 핸들값이 중요</t>
+  </si>
+  <si>
+    <t>//w를 앞에 붙이는 이유는 유니코드를 사용하기 위해서(즉, 안붙여도 동작은 됨) 매크로(조건부 컴파일이 안되있기 때문에)</t>
+  </si>
+  <si>
+    <t>AllocConsole();</t>
+  </si>
+  <si>
+    <t>WndClass.hbrBackground = (HBRUSH)GetStockObject(WHITE_BRUSH); //window 창 배경색(white,black,gray만 존재)</t>
+  </si>
+  <si>
+    <t>hWnd = CreateWindow(lpszClass2, lpszClass, WS_OVERLAPPEDWINDOW, CW_USEDEFAULT, CW_USEDEFAULT, CW_USEDEFAULT, CW_USEDEFAULT, NULL, NULL, g_hinst, NULL);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hTimer = (HANDLE)SetTimer(hWnd, 1, 1000, NULL); </t>
+  </si>
+  <si>
+    <t>hTimer2 = (HANDLE)SetTimer(hWnd, 2, 5000, NULL);</t>
+  </si>
+  <si>
+    <t>//프로그램 시작 1초 후에 타이머가 생기므로 그 공백을 없애기 위해서 SendMessage() 호출</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SendMessage(hWnd, WM_TIMER, 1, 0); </t>
+  </si>
+  <si>
+    <t>while (GetMessage(&amp;Message, NULL, 0, 0)) //메시지 루프(WM_QUIT을 제외하곤 TRUE를 리턴함으로 메시지루프 바디실행)</t>
+  </si>
+  <si>
+    <t>KillTimer(hWnd, 2);</t>
+  </si>
+  <si>
+    <t>static HANDLE hTimer, hTimer2;</t>
+  </si>
+  <si>
+    <t>SYSTEMTIME st;</t>
+  </si>
+  <si>
+    <t>static WCHAR sTimer[128];</t>
+  </si>
+  <si>
+    <t>static RECT rt = { 100,100,400,120 };</t>
+  </si>
+  <si>
+    <t>switch (iMessage) { //WM_CREATE,WM_DESTORY 일부 작업을 winMain으로 옮김</t>
+  </si>
+  <si>
+    <t>//hTimer = (HANDLE)SetTimer(hWnd, 1, 1000, NULL);</t>
+  </si>
+  <si>
+    <t>//hTimer2 = (HANDLE)SetTimer(hWnd, 2, 5000, NULL);</t>
+  </si>
+  <si>
+    <t>switch (wParam) {</t>
+  </si>
+  <si>
+    <t>GetLocalTime(&amp;st);</t>
+  </si>
+  <si>
+    <t>//문자열 포멧을 만들어서 첫번째 매개변수(sTimer)에 저장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wsprintf(sTimer, L"지금 시간은 %d%d%d입니다", st.wHour, st.wMinute, st.wSecond); </t>
+  </si>
+  <si>
+    <t>InvalidateRect(hWnd, &amp;rt, TRUE);</t>
+  </si>
+  <si>
+    <t>case 2:</t>
+  </si>
+  <si>
+    <t>TextOut(hdc, 100, 100, sTimer, wcslen(sTimer));</t>
+  </si>
+  <si>
+    <t>//KillTimer(hWnd, 1);</t>
+  </si>
+  <si>
+    <t>//KillTimer(hWnd, 2);</t>
   </si>
 </sst>
 </file>
@@ -4451,7 +4549,7 @@
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.4">
@@ -4466,22 +4564,22 @@
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A318" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A322" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -4548,7 +4646,7 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>246</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4559,7 +4657,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04728EDB-B3A1-4993-B993-BD89C0E92753}">
-  <dimension ref="A1:M321"/>
+  <dimension ref="A1:M428"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -5333,7 +5431,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.4">
@@ -5363,22 +5461,22 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B201" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B202" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B203" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B204" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.4">
@@ -5393,87 +5491,90 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C208" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="209" spans="2:3" x14ac:dyDescent="0.4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="209" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C209" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.4">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C210" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="211" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C211" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="212" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="212" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B212" t="s">
+        <v>251</v>
+      </c>
+      <c r="D212" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="213" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C213" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="213" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C213" t="s">
+    <row r="214" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C214" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="214" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C214" t="s">
+    <row r="215" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C215" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="215" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C215" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="216" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="216" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C216" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="217" spans="2:3" x14ac:dyDescent="0.4">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="217" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C217" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="218" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="218" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B218" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="219" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="219" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C219" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="220" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="220" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C220" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="221" spans="2:3" x14ac:dyDescent="0.4">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="221" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C221" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="222" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="222" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C222" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="223" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="223" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B223" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="224" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="224" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C224" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.4">
@@ -5508,7 +5609,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.4">
@@ -5538,22 +5639,22 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B238" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B239" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B240" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="241" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B241" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="243" spans="2:4" x14ac:dyDescent="0.4">
@@ -5568,17 +5669,17 @@
     </row>
     <row r="245" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C245" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="246" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C246" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="247" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C247" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="248" spans="2:4" x14ac:dyDescent="0.4">
@@ -5593,52 +5694,52 @@
     </row>
     <row r="250" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B250" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="251" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C251" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="252" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C252" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="253" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D253" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="254" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D254" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="255" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D255" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="256" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D256" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="257" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C257" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="258" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D258" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="259" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D259" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="260" spans="2:4" x14ac:dyDescent="0.4">
@@ -5648,7 +5749,7 @@
     </row>
     <row r="262" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C262" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="263" spans="2:4" x14ac:dyDescent="0.4">
@@ -5668,7 +5769,7 @@
     </row>
     <row r="266" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C266" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="267" spans="2:4" x14ac:dyDescent="0.4">
@@ -5688,12 +5789,12 @@
     </row>
     <row r="270" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C270" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="271" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C271" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="272" spans="2:4" x14ac:dyDescent="0.4">
@@ -5728,27 +5829,27 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B282" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B283" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.4">
@@ -5758,12 +5859,12 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B285" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C286" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.4">
@@ -5818,22 +5919,22 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C301" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C302" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B303" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C304" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="305" spans="2:4" x14ac:dyDescent="0.4">
@@ -5848,27 +5949,27 @@
     </row>
     <row r="307" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C307" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="308" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C308" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="309" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D309" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="310" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D310" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="311" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C311" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="312" spans="2:4" x14ac:dyDescent="0.4">
@@ -5888,7 +5989,7 @@
     </row>
     <row r="315" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C315" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="316" spans="2:4" x14ac:dyDescent="0.4">
@@ -5916,8 +6017,477 @@
         <v>129</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A323" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A324" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A325" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A327" t="s">
+        <v>131</v>
+      </c>
+      <c r="M327" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A328" t="s">
+        <v>78</v>
+      </c>
+      <c r="J328" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A329" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A330" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A331" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A332" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A333" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A334" t="s">
+        <v>83</v>
+      </c>
+      <c r="B334" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B336" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="337" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B337" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="339" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B339" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="340" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B340" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="341" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B341" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="342" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B342" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="344" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B344" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="345" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B345" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="346" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B346" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="347" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B347" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="348" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B348" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="349" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B349" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="350" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B350" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="351" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B351" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="352" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B352" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="353" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B353" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="354" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B354" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="356" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B356" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="358" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B358" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="359" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B359" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="360" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B360" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="361" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B361" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="362" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B362" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="364" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B364" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="366" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B366" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="367" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B367" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="368" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B368" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B369" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B370" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B372" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B373" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C375" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C376" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B377" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B378" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B379" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B380" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B381" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B382" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A383" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A385" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A386" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A387" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B388" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B389" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B390" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B391" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B392" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B393" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B395" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B397" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C398" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C399" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C400" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="401" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B401" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="402" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C402" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="404" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C404" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="405" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D405" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="406" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D406" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="407" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D407" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="408" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D408" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="409" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D409" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="410" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C410" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="411" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D411" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="412" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D412" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="413" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C413" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="414" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C414" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="415" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B415" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="416" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C416" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C417" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C418" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C419" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B420" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C421" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C422" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C423" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C424" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C425" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B426" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B427" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A428" t="s">
         <v>90</v>
       </c>
     </row>

--- a/windows_API.xlsx
+++ b/windows_API.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2FF26F-92C4-4DE5-B25B-273E64E1ABD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E928699-9BDA-4C33-99F7-BD0EA2756327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
   </bookViews>
   <sheets>
     <sheet name="기초개념" sheetId="1" r:id="rId1"/>
-    <sheet name="WM_MSG 정리" sheetId="3" r:id="rId2"/>
-    <sheet name="기본 동작 방식" sheetId="2" r:id="rId3"/>
+    <sheet name="리소스" sheetId="4" r:id="rId2"/>
+    <sheet name="WM_MSG 정리" sheetId="3" r:id="rId3"/>
+    <sheet name="기본 동작 방식" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="360">
   <si>
     <t xml:space="preserve">1. Windows SDK (Software Deveopment Kit) </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -569,18 +570,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3. WM_DESTORY : 창의 X버튼을 눌렀을때 발송</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5. WM_QUIT : PostQuitMessage(0)가 호출될때 발송</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. WM_CREATE : 윈도우창이 처음 생겼을때 발송(Unity의 start이벤트 메서드랑 유사)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GetDC(hWnd) : 클라이언트 좌표계 기준의 DC를 반환함,메시지와 무관하게(PAINT에서도 사용가능) 아무데서나 사용가능</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1163,13 +1152,152 @@
   </si>
   <si>
     <t>//KillTimer(hWnd, 2);</t>
+  </si>
+  <si>
+    <t>4. WM_CREATE : 윈도우창이 처음 생겼을때CreateWindow()호출되서 창이 생성될때) 발송(Unity의 start이벤트 메서드랑 유사)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. WM_DESTORY : 창의 X버튼을 눌렀을때 발송, (주로 PostQuitMessage(0)를 내부에서 호출 해서 WM_QUIT이 발송됨)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. WM_QUIT : PostQuitMessage(0)가 호출될때 발송, 메시지루프에서 이 메시지가 해석되고 false를 리턴해서 프로그램 종료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetClientRect(HWND, hWnd, LPRECT lpRect); 2번째 매개변수에 rect정보를 저장한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>static RECT rt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">//GetClientRect(hWnd, &amp;rt); </t>
+  </si>
+  <si>
+    <t>//창사이즈가 달라지거나 무효화 영역이 생기면, CREATE 안에선 처음정보만 가지고 있기 떄문에 rt값이 안변하지만</t>
+  </si>
+  <si>
+    <t>//PAINT는 무효화영역이 생길때마다 호출되기때문에 창 사이즈가 변할떄마다 변한 창사이즈의 rt값을 받아올 수 있다.</t>
+  </si>
+  <si>
+    <t>SetTextAlign(hdc, TA_CENTER);</t>
+  </si>
+  <si>
+    <t>TextOut(hdc, rt.right / 2, rt.bottom / 2, L"Center String", 13);</t>
+  </si>
+  <si>
+    <t>GetClientRect(hWnd, &amp;rt); //WM_CREATE가 아니라 WM_PAINT에서 호출한 이유:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetClientRect() 예제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11. WM_SIZE : 윈도우창의 크기가 변할때 발송(lParam의 상위 워드에는 높이,하위 워드에는 변경된 후의 윈도우 폭이, wParam에는 메시지가 발생한 이유를 플래그로 전달(102P에 플래그 목록))</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WM_SIZE 예제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>case WM_SIZE :</t>
+  </si>
+  <si>
+    <t>GetClientRect(hWnd, &amp;rt);</t>
+  </si>
+  <si>
+    <t>//printf("%d %d\n",LOWORD(lParam), HIWORD(lParam));</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InvalidateRect(hWnd, NULL, TRUE); </t>
+  </si>
+  <si>
+    <t>//rt값을 구하고 난뒤에 출력하기 위해 호출함.(구하기 전에 출력된 문자열도 같이 삭제)</t>
+  </si>
+  <si>
+    <t>12.WM_MOVE : 윈도우창이 이동될때(기준점은 좌상 꼭짓점) 발송됨(lParam의 상위워드엔 새 Y좌표가, 하위워드엔 새 X좌표가 전달됨)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. vs studio에서 리소스 파일 만드는법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-1 리소스 추가하기 : 프로젝트 명 우클릭 &gt;  Add &gt; Resource 클릭 &gt; 원하는 리소스 종류 선택 후 new 클릭(Header files에 Resource.h 파일, Resource Files에 선택한 리소스 파일과  .rc파일 추가)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 리소스 : gui의 재료가 되는 준비물(ex : 유니티의 assets)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.메뉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)최상단 메뉴는 ID가 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴 예제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#include "resource.h" //resource를 사용하면 include 해야함</t>
+  </si>
+  <si>
+    <t>WndClass.lpszMenuName = MAKEINTRESOURCE(IDR_MENU1); //메뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case WM_COMMAND: </t>
+  </si>
+  <si>
+    <t>//어떤 윈도우 창의 자식들(ex : 메뉴)에 이벤트가 발생했을때</t>
+  </si>
+  <si>
+    <t>//부모쪽으로 전달되는 메시지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">switch (LOWORD(wParam)) </t>
+  </si>
+  <si>
+    <t>case ID_FILE_OPEN: //메뉴의 세부메뉴의 ID</t>
+  </si>
+  <si>
+    <t>MessageBox(hWnd, L"첫번째 메뉴", L"Menu Demo", MB_OK);</t>
+  </si>
+  <si>
+    <t>case ID_FILE_EXIT: //메뉴의 세부메뉴의 ID</t>
+  </si>
+  <si>
+    <t>DestroyWindow(hWnd); //WM_DESTROY 호출</t>
+  </si>
+  <si>
+    <t>4. Resource View  창 : 리소스정보(이름,id 등)을 확인하는 창(세부정보는 .rc파일이나 resource.h에서 view code를 통해 확인)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. Prpertites 창 : 각 리소스의 세부 정보를 보여주거나 설정하는 창(ex: 캡션,id등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. resource.h 파일 : 좌측에 Id명, 우측에 id값이 기호상수로 저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. .rc파일 : 리소스 전반에 대한 정보를 알려주는 파일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1180,6 +1308,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -1208,12 +1344,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3377,6 +3516,433 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>454809</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>175261</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBD7A68B-FFD6-E3BD-DB25-2145FDE2191C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="220981"/>
+          <a:ext cx="4478169" cy="3268980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>178015</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15C6AB88-88C8-73C0-5028-117AA815A3B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4198620"/>
+          <a:ext cx="4442460" cy="4818595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>454809</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F81465D8-EE1A-4915-9716-E4EFC7921CC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4693920" y="4419600"/>
+          <a:ext cx="4478169" cy="3268980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>464820</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>201692</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F355039D-89FD-037C-4AE9-8F5BE0D69DF7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9723120"/>
+          <a:ext cx="8511540" cy="2853452"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>448920</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>90900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>192240</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>175560</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="6" name="잉크 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1279327F-AE52-AB04-D10D-F81FCB801E58}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="6483960" y="11360880"/>
+            <a:ext cx="1755000" cy="305640"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="6" name="잉크 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1279327F-AE52-AB04-D10D-F81FCB801E58}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6474960" y="11352240"/>
+              <a:ext cx="1772640" cy="323280"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>342901</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>61763</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{879451D8-1524-515A-EB49-48101F86883D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="13479780"/>
+          <a:ext cx="5036820" cy="3818423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>631026</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF226978-CBFB-7028-F0D5-D91493EE2567}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="17678400"/>
+          <a:ext cx="8007186" cy="3970020"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>333297</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>137161</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="그림 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFD82BA7-C7C9-3467-F100-80370761B78E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="22098001"/>
+          <a:ext cx="7038897" cy="4556760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>154555</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A636CA62-50E0-365B-4A03-BADF4981F82E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4861561"/>
+          <a:ext cx="5044440" cy="1922394"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>77035</xdr:rowOff>
     </xdr:from>
@@ -3462,6 +4028,34 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-05-19T10:20:50.151"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">3261 679 24575,'-401'-31'0,"175"7"0,10 5 0,-242-15 0,251 28 0,-382-7 0,-369 13 0,943 0 0,1 0 0,0-1 0,0 0 0,0-1 0,0-1 0,0 0 0,0-1 0,0-1 0,-15-7 0,25 9 0,0 0 0,0-1 0,1 0 0,-1 1 0,1-1 0,0-1 0,0 1 0,1 0 0,-1-1 0,1 1 0,0-1 0,0 0 0,0 1 0,1-1 0,0 0 0,0 0 0,-1-7 0,0-3 0,1-1 0,0 0 0,1 0 0,3-21 0,-2 26 0,1 1 0,0-1 0,1 1 0,0 0 0,1 0 0,0 0 0,0 0 0,1 0 0,12-17 0,-6 15 0,0-1 0,0 1 0,1 1 0,1 0 0,23-15 0,-2 1 0,-3 3 0,48-27 0,-67 43 0,0 0 0,1 1 0,0 1 0,-1 0 0,1 1 0,0 0 0,27-2 0,413 15 0,-123 3 0,-51 8 0,-10 0 0,-217-18 0,0 3 0,100 25 0,-11-1 0,464 49 0,-524-70 0,60 2 0,157-10 0,-135-3 0,-96 1 0,16 0 0,131 15 0,0 13 0,364-2 0,-555-26 0,0-1 0,27-7 0,-23 4 0,-22 5 0,1-1 0,0 1 0,-1 0 0,1 1 0,0-1 0,-1 1 0,1 0 0,-1 0 0,1 1 0,-1 0 0,9 4 0,-4-1 0,-1 0 0,0 0 0,0 1 0,-1 0 0,12 11 0,-18-15 0,1 0 0,-1 1 0,0-1 0,0 1 0,0 0 0,0-1 0,-1 1 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,-1 0 0,1 1 0,0-1 0,-1 0 0,0 0 0,1 1 0,-1-1 0,-1 0 0,1 0 0,0 1 0,-1-1 0,0 0 0,1 0 0,-1 0 0,-1 0 0,1 0 0,0 0 0,-3 5 0,-1 0 0,0-1 0,-1 0 0,1 0 0,-1 0 0,0-1 0,-1 1 0,0-2 0,0 1 0,0-1 0,-9 5 0,-107 53 0,-13 8 0,93-46 0,12-4 0,-2-2 0,0-2 0,-1-1 0,-70 23 0,61-31 0,-75 3 0,57-6 0,-86 15 0,87-10 0,-114 4 0,-280-15 0,419-1 0,-40-7 0,-22-1 0,5 10 0,-31-1 0,116 0-124,0-1 0,0 0 0,0 0 0,0 0 0,1-1 0,-1 0-1,1-1 1,-1 1 0,1-1 0,-10-8 0,6 2-6702</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3761,7 +4355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE0ACE2-906B-4F5F-9E70-EA3E758911EF}">
-  <dimension ref="A1:L322"/>
+  <dimension ref="A1:L324"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -4128,7 +4722,7 @@
         <v>98</v>
       </c>
       <c r="K143" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.4">
@@ -4166,22 +4760,22 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C202" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C203" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C208" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C209" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.4">
@@ -4201,7 +4795,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.4">
@@ -4231,57 +4825,57 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.4">
@@ -4306,27 +4900,27 @@
     </row>
     <row r="243" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B243" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="244" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B244" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="245" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C245" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="246" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C246" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="247" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C247" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="249" spans="2:9" x14ac:dyDescent="0.4">
@@ -4346,7 +4940,7 @@
     </row>
     <row r="252" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C252" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="253" spans="2:9" x14ac:dyDescent="0.4">
@@ -4356,7 +4950,7 @@
     </row>
     <row r="254" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C254" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="255" spans="2:9" x14ac:dyDescent="0.4">
@@ -4366,20 +4960,20 @@
     </row>
     <row r="256" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C256" t="s">
+        <v>206</v>
+      </c>
+      <c r="I256" t="s">
         <v>209</v>
-      </c>
-      <c r="I256" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C257" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C258" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.4">
@@ -4424,42 +5018,42 @@
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B286" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.4">
@@ -4469,117 +5063,122 @@
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A288" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A298" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A305" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A306" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A307" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A310" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A316" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A318" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A322" t="s">
-        <v>289</v>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A324" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -4590,74 +5189,145 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13244596-96F8-47E0-A9D7-E86B98AFFA18}">
-  <dimension ref="A1:A20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E03F252C-7D3D-43FC-9BAD-0E75F8A41803}">
+  <dimension ref="A1:P100"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>167</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>291</v>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="P58" s="2"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13244596-96F8-47E0-A9D7-E86B98AFFA18}">
+  <dimension ref="A1:A33"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04728EDB-B3A1-4993-B993-BD89C0E92753}">
-  <dimension ref="A1:M428"/>
+  <dimension ref="A1:M589"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -4690,7 +5360,7 @@
         <v>131</v>
       </c>
       <c r="M25" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -4698,7 +5368,7 @@
         <v>78</v>
       </c>
       <c r="J26" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -4726,7 +5396,7 @@
         <v>83</v>
       </c>
       <c r="B32" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
@@ -5001,32 +5671,32 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.4">
@@ -5051,12 +5721,12 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B110" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B111" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.4">
@@ -5076,17 +5746,17 @@
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C115" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B116" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C117" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.4">
@@ -5096,7 +5766,7 @@
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D119" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.4">
@@ -5106,27 +5776,27 @@
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C121" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D122" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D123" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D124" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D125" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.4">
@@ -5136,7 +5806,7 @@
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C127" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="128" spans="2:4" x14ac:dyDescent="0.4">
@@ -5156,7 +5826,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C131" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.4">
@@ -5206,12 +5876,12 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.4">
@@ -5236,12 +5906,12 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B151" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B152" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.4">
@@ -5261,27 +5931,27 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C156" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B157" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C158" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C159" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C160" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.4">
@@ -5291,42 +5961,42 @@
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B162" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C163" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D164" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D165" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D166" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D167" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D168" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D169" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.4">
@@ -5341,12 +6011,12 @@
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B172" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C173" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.4">
@@ -5356,12 +6026,12 @@
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B175" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C176" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.4">
@@ -5381,7 +6051,7 @@
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C180" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.4">
@@ -5431,12 +6101,12 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.4">
@@ -5461,22 +6131,22 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B201" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B202" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B203" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B204" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.4">
@@ -5491,12 +6161,12 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C208" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="209" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C209" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="210" spans="2:4" x14ac:dyDescent="0.4">
@@ -5506,35 +6176,35 @@
     </row>
     <row r="211" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C211" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="212" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B212" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D212" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="213" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C213" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="214" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C214" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="215" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C215" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="216" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C216" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="217" spans="2:4" x14ac:dyDescent="0.4">
@@ -5554,7 +6224,7 @@
     </row>
     <row r="220" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C220" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="221" spans="2:4" x14ac:dyDescent="0.4">
@@ -5574,7 +6244,7 @@
     </row>
     <row r="224" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C224" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.4">
@@ -5609,12 +6279,12 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.4">
@@ -5639,22 +6309,22 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B238" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B239" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B240" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="241" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B241" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="243" spans="2:4" x14ac:dyDescent="0.4">
@@ -5669,17 +6339,17 @@
     </row>
     <row r="245" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C245" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="246" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C246" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="247" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C247" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="248" spans="2:4" x14ac:dyDescent="0.4">
@@ -5689,57 +6359,57 @@
     </row>
     <row r="249" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C249" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="250" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B250" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="251" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C251" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="252" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C252" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="253" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D253" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="254" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D254" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="255" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D255" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="256" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D256" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="257" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C257" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="258" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D258" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="259" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D259" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="260" spans="2:4" x14ac:dyDescent="0.4">
@@ -5749,7 +6419,7 @@
     </row>
     <row r="262" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C262" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="263" spans="2:4" x14ac:dyDescent="0.4">
@@ -5769,7 +6439,7 @@
     </row>
     <row r="266" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C266" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="267" spans="2:4" x14ac:dyDescent="0.4">
@@ -5789,12 +6459,12 @@
     </row>
     <row r="270" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C270" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="271" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C271" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="272" spans="2:4" x14ac:dyDescent="0.4">
@@ -5829,42 +6499,42 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B282" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B283" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B284" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B285" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C286" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.4">
@@ -5874,7 +6544,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B288" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.4">
@@ -5884,7 +6554,7 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.4">
@@ -5919,22 +6589,22 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C301" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C302" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B303" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C304" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="305" spans="2:4" x14ac:dyDescent="0.4">
@@ -5949,27 +6619,27 @@
     </row>
     <row r="307" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C307" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="308" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C308" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="309" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D309" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="310" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D310" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="311" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C311" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="312" spans="2:4" x14ac:dyDescent="0.4">
@@ -5989,7 +6659,7 @@
     </row>
     <row r="315" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C315" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="316" spans="2:4" x14ac:dyDescent="0.4">
@@ -6024,7 +6694,7 @@
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.4">
@@ -6042,7 +6712,7 @@
         <v>131</v>
       </c>
       <c r="M327" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.4">
@@ -6050,7 +6720,7 @@
         <v>78</v>
       </c>
       <c r="J328" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.4">
@@ -6070,12 +6740,12 @@
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A332" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.4">
@@ -6083,12 +6753,12 @@
         <v>83</v>
       </c>
       <c r="B334" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B336" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="337" spans="2:2" x14ac:dyDescent="0.4">
@@ -6133,7 +6803,7 @@
     </row>
     <row r="347" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B347" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="348" spans="2:2" x14ac:dyDescent="0.4">
@@ -6178,7 +6848,7 @@
     </row>
     <row r="358" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B358" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="359" spans="2:2" x14ac:dyDescent="0.4">
@@ -6208,22 +6878,22 @@
     </row>
     <row r="366" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B366" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="367" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B367" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="368" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B368" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B369" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.4">
@@ -6233,7 +6903,7 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B372" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.4">
@@ -6268,12 +6938,12 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B380" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B381" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.4">
@@ -6288,7 +6958,7 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A385" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.4">
@@ -6313,27 +6983,27 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B390" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B391" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B392" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B393" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B395" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.4">
@@ -6343,72 +7013,72 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C398" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C399" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C400" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="401" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B401" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="402" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C402" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="404" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C404" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="405" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D405" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="406" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D406" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="407" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D407" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="408" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D408" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="409" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D409" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="410" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C410" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="411" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D411" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="412" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D412" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="413" spans="2:4" x14ac:dyDescent="0.4">
@@ -6433,7 +7103,7 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C417" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.4">
@@ -6453,12 +7123,12 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C421" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C422" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.4">
@@ -6488,6 +7158,685 @@
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A428" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A430" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A432" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A433" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A434" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B435" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B436" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B437" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B439" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B440" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C441" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C442" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B444" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C445" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C446" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C447" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C448" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C449" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C450" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C451" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C452" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B453" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C454" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C455" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C456" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C457" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B458" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B459" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A460" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A462" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A464" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A465" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A466" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B467" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B468" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B469" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B471" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B472" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C473" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C474" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B476" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C477" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C478" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C479" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C480" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C481" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B482" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C483" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C484" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C485" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C486" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C487" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B488" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C489" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C490" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C491" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C492" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B493" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B494" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A495" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="497" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A497" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="499" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A499" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="500" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A500" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="501" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A501" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="503" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A503" t="s">
+        <v>131</v>
+      </c>
+      <c r="M503" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="504" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A504" t="s">
+        <v>78</v>
+      </c>
+      <c r="J504" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="505" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A505" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="506" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A506" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="507" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A507" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="509" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A509" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="510" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A510" t="s">
+        <v>83</v>
+      </c>
+      <c r="B510" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="512" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B512" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="513" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B513" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="515" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B515" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="516" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B516" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="517" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B517" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="518" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B518" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="520" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B520" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="521" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B521" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="522" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B522" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="523" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B523" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="524" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B524" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="525" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B525" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="526" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B526" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="527" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B527" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="528" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B528" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="529" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B529" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="530" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B530" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="532" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B532" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="534" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B534" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="535" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B535" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="536" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B536" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="537" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B537" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="538" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B538" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="540" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B540" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="542" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B542" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="544" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B544" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B545" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C547" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C548" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B549" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B550" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B551" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B552" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A553" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A555" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A556" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A557" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B558" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B559" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B560" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="562" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B562" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="563" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B563" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="564" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C564" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="565" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C565" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="566" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C566" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="567" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C567" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="568" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C568" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="569" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D569" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="570" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D570" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="572" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C572" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="573" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D573" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="574" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D574" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="575" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C575" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B578" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C579" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C580" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B582" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C583" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C584" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C585" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C586" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B587" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B588" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A589" t="s">
         <v>90</v>
       </c>
     </row>

--- a/windows_API.xlsx
+++ b/windows_API.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E928699-9BDA-4C33-99F7-BD0EA2756327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D749065B-C66F-4C7A-A917-AD3B5B49F37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{1C61B221-D19C-422C-9F30-EAB69C5BE3FA}"/>
   </bookViews>
   <sheets>
     <sheet name="기초개념" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="373">
   <si>
     <t xml:space="preserve">1. Windows SDK (Software Deveopment Kit) </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1291,6 +1291,56 @@
   <si>
     <t>7. .rc파일 : 리소스 전반에 대한 정보를 알려주는 파일</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13. WM_COMMAND : 어떤 윈도우 창의 자식들(ex : 메뉴)에 이벤트가 발생했을때 부모쪽으로 전달되는 메시지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)lParam : 통지 메시지를 발생시킨 컨트롤의 윈도우 핸들</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)LOWORD(wParam) : 메뉴나 엑셀러레이터, 컨트롤의 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)HIWORD(wParam) : 컨트롤이 보내주는 통지 메시지, 메뉴가 선택된 경우는 0이 되며 엑셀러레이터가 선택된 경우는 1이 된다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)소스코드에서 캡션 아이콘 바꾸기 : WndClass.hIcon = LoadIconW(hinstance, MAKEINTRESOURCE(IDI_ICON1));</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.icon &amp; 커서만들기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)등록하기 : .rc파일에서 우클릭 &gt; add resource &gt; icon 선택 &gt; import로 만들어둔 아이콘 파일 선택(커서는 cursor 선택후 import)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4)소스코드에서 커서 바꾸기 : WndClass.hCursor = LoadCursorW(hinstance, MAKEINTRESOURCE(IDC_CURSOR1));</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)icon 파일(이미지) 만들기 : greenfish Icon edtior pro같은 이미지 에디터를 인스톨한후, new graphic로 사이즈 설정후 아이콘 제작 &gt; 저장할때 파일형식이 Windows icon files로 저장(커서도 동일한 방식하되, 파일형식을 비트맵으로 저장)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1-1)커서는 비주얼 스튜디오에서도 자체 제작 가능(.rc파일에서 우클릭 &gt; add resource &gt; curosr 선택 &gt; new &gt; 에디터에서 제작 후 저장)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>커서랑 캡션 아이콘 예제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WndClass.hCursor = LoadCursorW(hinstance, MAKEINTRESOURCE(IDC_CURSOR1)); //커서 모양 설정(2번째 매개변수에 커서 ID입력)</t>
+  </si>
+  <si>
+    <t>WndClass.hIcon = LoadIconW(hinstance, MAKEINTRESOURCE(IDI_ICON1)); //캡션아이콘(창이름 옆에 있는) 설정</t>
   </si>
 </sst>
 </file>
@@ -3701,8 +3751,8 @@
       <xdr:row>52</xdr:row>
       <xdr:rowOff>175560</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="6" name="잉크 5">
@@ -3721,7 +3771,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="6" name="잉크 5">
@@ -3877,6 +3927,50 @@
         <a:xfrm>
           <a:off x="0" y="22098001"/>
           <a:ext cx="7038897" cy="4556760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>141922</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>52258</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="그림 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98570A9E-B4A5-A19E-9AA2-E859D4BFB773}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="27409140"/>
+          <a:ext cx="5506402" cy="3580318"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5190,7 +5284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E03F252C-7D3D-43FC-9BAD-0E75F8A41803}">
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:P145"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -5239,6 +5333,36 @@
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
         <v>359</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A143" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A144" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A145" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -5250,7 +5374,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13244596-96F8-47E0-A9D7-E86B98AFFA18}">
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -5316,6 +5440,26 @@
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>339</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -5327,7 +5471,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04728EDB-B3A1-4993-B993-BD89C0E92753}">
-  <dimension ref="A1:M589"/>
+  <dimension ref="A1:M683"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -7837,6 +7981,390 @@
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A589" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A591" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A592" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="593" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A593" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="594" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A594" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="596" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A596" t="s">
+        <v>131</v>
+      </c>
+      <c r="M596" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="597" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A597" t="s">
+        <v>78</v>
+      </c>
+      <c r="J597" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="598" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A598" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="599" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A599" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="600" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A600" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="602" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A602" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="603" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A603" t="s">
+        <v>83</v>
+      </c>
+      <c r="B603" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="605" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B605" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="606" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B606" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="608" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B608" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="609" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B609" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="610" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B610" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="611" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B611" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="613" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B613" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="614" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B614" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="615" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B615" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="616" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B616" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="617" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B617" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="618" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B618" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="619" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B619" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="620" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B620" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="621" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B621" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="622" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B622" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="623" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B623" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="626" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B626" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="628" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B628" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="629" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B629" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="630" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B630" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="631" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B631" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="632" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B632" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="634" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B634" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="636" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B636" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="638" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B638" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="639" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B639" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C641" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C642" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B643" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B644" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B645" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B646" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A647" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A649" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A650" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A651" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B652" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B653" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B654" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B656" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="657" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B657" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="658" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C658" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="659" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C659" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="660" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C660" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="661" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C661" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="662" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C662" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="663" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D663" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="664" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D664" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="666" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C666" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="667" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D667" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="668" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D668" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="669" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C669" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="672" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B672" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C673" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C674" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B676" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C677" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C678" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C679" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C680" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B681" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B682" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A683" t="s">
         <v>90</v>
       </c>
     </row>
